--- a/01_Befolkning/Befolkningsframskrivinger/Diverse befolkningsframskrivinger.xlsx
+++ b/01_Befolkning/Befolkningsframskrivinger/Diverse befolkningsframskrivinger.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vestfoldfylke-my.sharepoint.com/personal/kjetil_gunnerud_kristoffersen_vestfoldfylke_no/Documents/Dokumenter/GitHub2/Vestfold/01_Befolkning/Befolkningsframskrivinger/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vestfoldfylke-my.sharepoint.com/personal/rasmus_palmqvist_vestfoldfylke_no/Documents/Dokumenter/GitHub/Ny mappe/Vestfold/01_Befolkning/Befolkningsframskrivinger/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5B31AB13-E86D-463D-90A3-187EE6EE97F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="202" documentId="8_{5B31AB13-E86D-463D-90A3-187EE6EE97F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{924246BB-98D1-4B02-950C-5CEA647869E2}"/>
   <bookViews>
-    <workbookView xWindow="-19305" yWindow="-5490" windowWidth="19410" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fodt" sheetId="2" r:id="rId1"/>
+    <sheet name="Befolkningsframskrivinger 2026" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="92">
   <si>
     <t>14289: Framskrevne befolkningsendringer, etter region, år, statistikkvariabel og alternativ</t>
   </si>
@@ -303,6 +303,15 @@
   <si>
     <t>67 år eller eldre</t>
   </si>
+  <si>
+    <t>14747: Framskrevne befolkningsendringer, etter region, år og alternativ</t>
+  </si>
+  <si>
+    <t>Befolkning 2026</t>
+  </si>
+  <si>
+    <t>Sum</t>
+  </si>
 </sst>
 </file>
 
@@ -311,7 +320,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -335,6 +344,18 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF162327"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -366,7 +387,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -380,9 +401,9 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -687,20 +708,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:V238"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="7" width="9.1796875" customWidth="1"/>
+    <col min="1" max="4" width="9.140625" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" customWidth="1"/>
+    <col min="7" max="7" width="16.85546875" customWidth="1"/>
+    <col min="13" max="13" width="13.5703125" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:22" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="E3" s="2"/>
     </row>
-    <row r="4" spans="1:22" ht="29" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:22" ht="45" x14ac:dyDescent="0.25">
       <c r="C4" s="2" t="s">
         <v>1</v>
       </c>
@@ -747,7 +773,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
@@ -807,7 +833,7 @@
         <v>7.0260209742653634</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
         <v>7</v>
       </c>
@@ -864,7 +890,7 @@
         <v>24.877195593926764</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
         <v>8</v>
       </c>
@@ -921,7 +947,7 @@
         <v>13.291310372798865</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
         <v>9</v>
       </c>
@@ -978,7 +1004,7 @@
         <v>11.416104241216349</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
         <v>10</v>
       </c>
@@ -1035,7 +1061,7 @@
         <v>8.2089705429539155</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
         <v>11</v>
       </c>
@@ -1092,7 +1118,7 @@
         <v>9.4469292025744522</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
         <v>12</v>
       </c>
@@ -1154,7 +1180,7 @@
         <v>11.960675734697698</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B12" s="2" t="s">
         <v>13</v>
       </c>
@@ -1177,7 +1203,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
         <v>14</v>
       </c>
@@ -1200,7 +1226,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
         <v>15</v>
       </c>
@@ -1223,7 +1249,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
         <v>16</v>
       </c>
@@ -1249,7 +1275,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
         <v>17</v>
       </c>
@@ -1305,7 +1331,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
         <v>18</v>
       </c>
@@ -1365,7 +1391,7 @@
         <v>29859</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="s">
         <v>19</v>
       </c>
@@ -1425,7 +1451,7 @@
         <v>33427</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B19" s="2" t="s">
         <v>20</v>
       </c>
@@ -1485,7 +1511,7 @@
         <v>66892</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B20" s="2" t="s">
         <v>21</v>
       </c>
@@ -1545,7 +1571,7 @@
         <v>73640</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B21" s="2" t="s">
         <v>22</v>
       </c>
@@ -1605,7 +1631,7 @@
         <v>52651</v>
       </c>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B22" s="2" t="s">
         <v>23</v>
       </c>
@@ -1665,7 +1691,7 @@
         <v>30052</v>
       </c>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B23" s="2" t="s">
         <v>24</v>
       </c>
@@ -1735,7 +1761,7 @@
         <v>286521</v>
       </c>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B24" s="2" t="s">
         <v>25</v>
       </c>
@@ -1765,7 +1791,7 @@
       <c r="P24" s="3"/>
       <c r="Q24" s="3"/>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B25" s="2" t="s">
         <v>26</v>
       </c>
@@ -1821,7 +1847,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B26" s="2" t="s">
         <v>27</v>
       </c>
@@ -1891,7 +1917,7 @@
         <v>26.534713151813524</v>
       </c>
     </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B27" s="2" t="s">
         <v>28</v>
       </c>
@@ -1961,7 +1987,7 @@
         <v>25.739671523020313</v>
       </c>
     </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B28" s="2" t="s">
         <v>29</v>
       </c>
@@ -2031,7 +2057,7 @@
         <v>25.186868384859174</v>
       </c>
     </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B29" s="2" t="s">
         <v>30</v>
       </c>
@@ -2101,7 +2127,7 @@
         <v>25.890820206409558</v>
       </c>
     </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B30" s="2" t="s">
         <v>31</v>
       </c>
@@ -2171,7 +2197,7 @@
         <v>27.786746690471215</v>
       </c>
     </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B31" s="2" t="s">
         <v>32</v>
       </c>
@@ -2241,7 +2267,7 @@
         <v>28.404099560761349</v>
       </c>
     </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>65</v>
       </c>
@@ -2312,7 +2338,7 @@
         <v>26.387943641129269</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>33</v>
       </c>
@@ -2338,7 +2364,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B34" s="2" t="s">
         <v>7</v>
       </c>
@@ -2361,7 +2387,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B35" s="2" t="s">
         <v>8</v>
       </c>
@@ -2384,7 +2410,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B36" s="2" t="s">
         <v>9</v>
       </c>
@@ -2406,15 +2432,11 @@
       <c r="H36" s="3">
         <v>336</v>
       </c>
-      <c r="K36" s="9"/>
-      <c r="L36" s="9"/>
-      <c r="M36" s="10" t="s">
+      <c r="M36" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="N36" s="9"/>
-      <c r="O36" s="9"/>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B37" s="2" t="s">
         <v>10</v>
       </c>
@@ -2436,19 +2458,17 @@
       <c r="H37" s="3">
         <v>311</v>
       </c>
-      <c r="K37" s="9"/>
-      <c r="L37" s="9"/>
-      <c r="M37" s="10" t="s">
+      <c r="M37" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="N37" s="10" t="s">
+      <c r="N37" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="O37" s="10" t="s">
+      <c r="O37" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B38" s="2" t="s">
         <v>11</v>
       </c>
@@ -2470,23 +2490,23 @@
       <c r="H38" s="3">
         <v>286</v>
       </c>
-      <c r="K38" s="10" t="s">
+      <c r="K38" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="L38" s="10" t="s">
+      <c r="L38" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="M38" s="11">
+      <c r="M38" s="3">
         <v>2084</v>
       </c>
-      <c r="N38" s="11">
+      <c r="N38" s="3">
         <v>2381</v>
       </c>
-      <c r="O38" s="11">
+      <c r="O38" s="3">
         <v>2245</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B39" s="2" t="s">
         <v>12</v>
       </c>
@@ -2508,21 +2528,20 @@
       <c r="H39" s="3">
         <v>282</v>
       </c>
-      <c r="K39" s="9"/>
-      <c r="L39" s="10" t="s">
+      <c r="L39" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="M39" s="11">
+      <c r="M39" s="3">
         <v>12224</v>
       </c>
-      <c r="N39" s="11">
+      <c r="N39" s="3">
         <v>12922</v>
       </c>
-      <c r="O39" s="11">
+      <c r="O39" s="3">
         <v>12464</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B40" s="2" t="s">
         <v>13</v>
       </c>
@@ -2544,21 +2563,20 @@
       <c r="H40" s="3">
         <v>277</v>
       </c>
-      <c r="K40" s="9"/>
-      <c r="L40" s="10" t="s">
+      <c r="L40" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="M40" s="11">
+      <c r="M40" s="3">
         <v>19973</v>
       </c>
-      <c r="N40" s="11">
+      <c r="N40" s="3">
         <v>18803</v>
       </c>
-      <c r="O40" s="11">
+      <c r="O40" s="3">
         <v>19483</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B41" s="2" t="s">
         <v>14</v>
       </c>
@@ -2580,21 +2598,20 @@
       <c r="H41" s="3">
         <v>271</v>
       </c>
-      <c r="K41" s="9"/>
-      <c r="L41" s="10" t="s">
+      <c r="L41" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="M41" s="11">
+      <c r="M41" s="3">
         <v>9486</v>
       </c>
-      <c r="N41" s="11">
+      <c r="N41" s="3">
         <v>8052</v>
       </c>
-      <c r="O41" s="11">
+      <c r="O41" s="3">
         <v>8750</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B42" s="2" t="s">
         <v>15</v>
       </c>
@@ -2616,21 +2633,20 @@
       <c r="H42" s="3">
         <v>265</v>
       </c>
-      <c r="K42" s="9"/>
-      <c r="L42" s="10" t="s">
+      <c r="L42" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="M42" s="11">
+      <c r="M42" s="3">
         <v>12489</v>
       </c>
-      <c r="N42" s="11">
+      <c r="N42" s="3">
         <v>10745</v>
       </c>
-      <c r="O42" s="11">
+      <c r="O42" s="3">
         <v>11251</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B43" s="2" t="s">
         <v>16</v>
       </c>
@@ -2652,21 +2668,20 @@
       <c r="H43" s="3">
         <v>259</v>
       </c>
-      <c r="K43" s="9"/>
-      <c r="L43" s="10" t="s">
+      <c r="L43" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="M43" s="11">
+      <c r="M43" s="3">
         <v>76097</v>
       </c>
-      <c r="N43" s="11">
+      <c r="N43" s="3">
         <v>76297</v>
       </c>
-      <c r="O43" s="11">
+      <c r="O43" s="3">
         <v>73237</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B44" s="2" t="s">
         <v>17</v>
       </c>
@@ -2688,21 +2703,20 @@
       <c r="H44" s="3">
         <v>256</v>
       </c>
-      <c r="K44" s="9"/>
-      <c r="L44" s="10" t="s">
+      <c r="L44" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="M44" s="11">
+      <c r="M44" s="3">
         <v>75919</v>
       </c>
-      <c r="N44" s="11">
+      <c r="N44" s="3">
         <v>80626</v>
       </c>
-      <c r="O44" s="11">
+      <c r="O44" s="3">
         <v>83484</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B45" s="2" t="s">
         <v>18</v>
       </c>
@@ -2724,21 +2738,20 @@
       <c r="H45" s="3">
         <v>246</v>
       </c>
-      <c r="K45" s="9"/>
-      <c r="L45" s="10" t="s">
+      <c r="L45" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="M45" s="11">
+      <c r="M45" s="3">
         <v>34934</v>
       </c>
-      <c r="N45" s="11">
+      <c r="N45" s="3">
         <v>43634</v>
       </c>
-      <c r="O45" s="11">
+      <c r="O45" s="3">
         <v>44511</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B46" s="2" t="s">
         <v>19</v>
       </c>
@@ -2760,21 +2773,20 @@
       <c r="H46" s="3">
         <v>238</v>
       </c>
-      <c r="K46" s="9"/>
-      <c r="L46" s="10" t="s">
+      <c r="L46" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="M46" s="11">
+      <c r="M46" s="3">
         <v>10944</v>
       </c>
-      <c r="N46" s="11">
+      <c r="N46" s="3">
         <v>19624</v>
       </c>
-      <c r="O46" s="11">
+      <c r="O46" s="3">
         <v>24365</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B47" s="2" t="s">
         <v>20</v>
       </c>
@@ -2796,21 +2808,20 @@
       <c r="H47" s="3">
         <v>230</v>
       </c>
-      <c r="K47" s="9"/>
-      <c r="L47" s="10" t="s">
+      <c r="L47" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="M47" s="11">
+      <c r="M47" s="3">
         <v>2282</v>
       </c>
-      <c r="N47" s="11">
+      <c r="N47" s="3">
         <v>4814</v>
       </c>
-      <c r="O47" s="11">
+      <c r="O47" s="3">
         <v>6731</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B48" s="2" t="s">
         <v>21</v>
       </c>
@@ -2832,20 +2843,20 @@
       <c r="H48" s="3">
         <v>222</v>
       </c>
-      <c r="M48" s="11">
+      <c r="M48" s="3">
         <f>SUM(M38:M47)</f>
         <v>256432</v>
       </c>
-      <c r="N48" s="11">
+      <c r="N48" s="3">
         <f t="shared" ref="N48:O48" si="11">SUM(N38:N47)</f>
         <v>277898</v>
       </c>
-      <c r="O48" s="11">
+      <c r="O48" s="3">
         <f t="shared" si="11"/>
         <v>286521</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B49" s="2" t="s">
         <v>22</v>
       </c>
@@ -2868,7 +2879,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B50" s="2" t="s">
         <v>23</v>
       </c>
@@ -2890,7 +2901,7 @@
       <c r="H50" s="3">
         <v>205</v>
       </c>
-      <c r="L50" s="10" t="s">
+      <c r="L50" s="2" t="s">
         <v>88</v>
       </c>
       <c r="M50" s="8">
@@ -2906,7 +2917,7 @@
         <v>0.26387943641129269</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B51" s="2" t="s">
         <v>24</v>
       </c>
@@ -2929,7 +2940,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B52" s="2" t="s">
         <v>25</v>
       </c>
@@ -2952,7 +2963,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B53" s="2" t="s">
         <v>26</v>
       </c>
@@ -2975,7 +2986,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B54" s="2" t="s">
         <v>27</v>
       </c>
@@ -2998,7 +3009,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B55" s="2" t="s">
         <v>28</v>
       </c>
@@ -3021,7 +3032,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B56" s="2" t="s">
         <v>29</v>
       </c>
@@ -3044,7 +3055,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B57" s="2" t="s">
         <v>30</v>
       </c>
@@ -3067,7 +3078,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B58" s="2" t="s">
         <v>31</v>
       </c>
@@ -3090,7 +3101,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B59" s="2" t="s">
         <v>32</v>
       </c>
@@ -3113,7 +3124,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>66</v>
       </c>
@@ -3137,7 +3148,7 @@
         <v>6685</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>34</v>
       </c>
@@ -3163,7 +3174,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B62" s="2" t="s">
         <v>7</v>
       </c>
@@ -3186,7 +3197,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B63" s="2" t="s">
         <v>8</v>
       </c>
@@ -3209,7 +3220,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B64" s="2" t="s">
         <v>9</v>
       </c>
@@ -3232,7 +3243,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="65" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B65" s="2" t="s">
         <v>10</v>
       </c>
@@ -3255,7 +3266,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="66" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B66" s="2" t="s">
         <v>11</v>
       </c>
@@ -3278,7 +3289,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="67" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B67" s="2" t="s">
         <v>12</v>
       </c>
@@ -3301,7 +3312,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="68" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B68" s="2" t="s">
         <v>13</v>
       </c>
@@ -3324,7 +3335,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="69" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B69" s="2" t="s">
         <v>14</v>
       </c>
@@ -3347,7 +3358,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="70" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B70" s="2" t="s">
         <v>15</v>
       </c>
@@ -3370,7 +3381,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="71" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B71" s="2" t="s">
         <v>16</v>
       </c>
@@ -3393,7 +3404,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="72" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B72" s="2" t="s">
         <v>17</v>
       </c>
@@ -3416,7 +3427,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="73" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B73" s="2" t="s">
         <v>18</v>
       </c>
@@ -3439,7 +3450,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="74" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B74" s="2" t="s">
         <v>19</v>
       </c>
@@ -3462,7 +3473,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="75" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B75" s="2" t="s">
         <v>20</v>
       </c>
@@ -3485,7 +3496,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="76" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B76" s="2" t="s">
         <v>21</v>
       </c>
@@ -3508,7 +3519,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="77" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B77" s="2" t="s">
         <v>22</v>
       </c>
@@ -3531,7 +3542,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="78" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B78" s="2" t="s">
         <v>23</v>
       </c>
@@ -3554,7 +3565,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="79" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B79" s="2" t="s">
         <v>24</v>
       </c>
@@ -3577,7 +3588,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="80" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B80" s="2" t="s">
         <v>25</v>
       </c>
@@ -3600,7 +3611,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B81" s="2" t="s">
         <v>26</v>
       </c>
@@ -3623,7 +3634,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B82" s="2" t="s">
         <v>27</v>
       </c>
@@ -3646,7 +3657,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B83" s="2" t="s">
         <v>28</v>
       </c>
@@ -3669,7 +3680,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B84" s="2" t="s">
         <v>29</v>
       </c>
@@ -3692,7 +3703,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B85" s="2" t="s">
         <v>30</v>
       </c>
@@ -3715,7 +3726,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B86" s="2" t="s">
         <v>31</v>
       </c>
@@ -3738,7 +3749,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B87" s="2" t="s">
         <v>32</v>
       </c>
@@ -3761,7 +3772,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B88" s="2"/>
       <c r="C88" s="3">
         <v>14758</v>
@@ -3782,7 +3793,7 @@
         <v>7865</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>35</v>
       </c>
@@ -3808,7 +3819,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B90" s="2" t="s">
         <v>7</v>
       </c>
@@ -3831,7 +3842,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B91" s="2" t="s">
         <v>8</v>
       </c>
@@ -3854,7 +3865,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B92" s="2" t="s">
         <v>9</v>
       </c>
@@ -3877,7 +3888,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B93" s="2" t="s">
         <v>10</v>
       </c>
@@ -3900,7 +3911,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B94" s="2" t="s">
         <v>11</v>
       </c>
@@ -3923,7 +3934,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B95" s="2" t="s">
         <v>12</v>
       </c>
@@ -3946,7 +3957,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B96" s="2" t="s">
         <v>13</v>
       </c>
@@ -3969,7 +3980,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="97" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="97" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B97" s="2" t="s">
         <v>14</v>
       </c>
@@ -3992,7 +4003,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="98" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="98" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B98" s="2" t="s">
         <v>15</v>
       </c>
@@ -4015,7 +4026,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="99" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="99" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B99" s="2" t="s">
         <v>16</v>
       </c>
@@ -4038,7 +4049,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="100" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="100" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B100" s="2" t="s">
         <v>17</v>
       </c>
@@ -4061,7 +4072,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="101" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="101" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B101" s="2" t="s">
         <v>18</v>
       </c>
@@ -4084,7 +4095,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="102" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="102" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B102" s="2" t="s">
         <v>19</v>
       </c>
@@ -4107,7 +4118,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="103" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="103" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B103" s="2" t="s">
         <v>20</v>
       </c>
@@ -4130,7 +4141,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="104" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="104" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B104" s="2" t="s">
         <v>21</v>
       </c>
@@ -4153,7 +4164,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="105" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="105" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B105" s="2" t="s">
         <v>22</v>
       </c>
@@ -4176,7 +4187,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="106" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="106" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B106" s="2" t="s">
         <v>23</v>
       </c>
@@ -4199,7 +4210,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="107" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="107" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B107" s="2" t="s">
         <v>24</v>
       </c>
@@ -4222,7 +4233,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="108" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="108" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B108" s="2" t="s">
         <v>25</v>
       </c>
@@ -4245,7 +4256,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="109" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="109" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B109" s="2" t="s">
         <v>26</v>
       </c>
@@ -4268,7 +4279,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="110" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="110" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B110" s="2" t="s">
         <v>27</v>
       </c>
@@ -4291,7 +4302,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="111" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="111" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B111" s="2" t="s">
         <v>28</v>
       </c>
@@ -4314,7 +4325,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="112" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="112" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B112" s="2" t="s">
         <v>29</v>
       </c>
@@ -4337,7 +4348,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B113" s="2" t="s">
         <v>30</v>
       </c>
@@ -4360,7 +4371,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B114" s="2" t="s">
         <v>31</v>
       </c>
@@ -4383,7 +4394,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B115" s="2" t="s">
         <v>32</v>
       </c>
@@ -4406,7 +4417,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B116" s="2"/>
       <c r="C116" s="3">
         <v>15444</v>
@@ -4427,7 +4438,7 @@
         <v>7561</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>36</v>
       </c>
@@ -4453,7 +4464,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B118" s="2" t="s">
         <v>7</v>
       </c>
@@ -4476,7 +4487,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B119" s="2" t="s">
         <v>8</v>
       </c>
@@ -4499,7 +4510,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B120" s="2" t="s">
         <v>9</v>
       </c>
@@ -4522,7 +4533,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B121" s="2" t="s">
         <v>10</v>
       </c>
@@ -4545,7 +4556,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B122" s="2" t="s">
         <v>11</v>
       </c>
@@ -4568,7 +4579,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B123" s="2" t="s">
         <v>12</v>
       </c>
@@ -4591,7 +4602,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B124" s="2" t="s">
         <v>13</v>
       </c>
@@ -4614,7 +4625,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B125" s="2" t="s">
         <v>14</v>
       </c>
@@ -4637,7 +4648,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B126" s="2" t="s">
         <v>15</v>
       </c>
@@ -4660,7 +4671,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B127" s="2" t="s">
         <v>16</v>
       </c>
@@ -4683,7 +4694,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B128" s="2" t="s">
         <v>17</v>
       </c>
@@ -4706,7 +4717,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="129" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="129" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B129" s="2" t="s">
         <v>18</v>
       </c>
@@ -4729,7 +4740,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="130" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="130" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B130" s="2" t="s">
         <v>19</v>
       </c>
@@ -4752,7 +4763,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="131" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="131" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B131" s="2" t="s">
         <v>20</v>
       </c>
@@ -4775,7 +4786,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="132" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="132" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B132" s="2" t="s">
         <v>21</v>
       </c>
@@ -4798,7 +4809,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="133" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="133" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B133" s="2" t="s">
         <v>22</v>
       </c>
@@ -4821,7 +4832,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="134" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="134" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B134" s="2" t="s">
         <v>23</v>
       </c>
@@ -4844,7 +4855,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="135" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="135" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B135" s="2" t="s">
         <v>24</v>
       </c>
@@ -4867,7 +4878,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="136" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="136" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B136" s="2" t="s">
         <v>25</v>
       </c>
@@ -4890,7 +4901,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="137" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="137" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B137" s="2" t="s">
         <v>26</v>
       </c>
@@ -4913,7 +4924,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="138" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="138" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B138" s="2" t="s">
         <v>27</v>
       </c>
@@ -4936,7 +4947,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="139" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="139" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B139" s="2" t="s">
         <v>28</v>
       </c>
@@ -4959,7 +4970,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="140" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="140" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B140" s="2" t="s">
         <v>29</v>
       </c>
@@ -4982,7 +4993,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="141" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="141" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B141" s="2" t="s">
         <v>30</v>
       </c>
@@ -5005,7 +5016,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="142" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="142" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B142" s="2" t="s">
         <v>31</v>
       </c>
@@ -5028,7 +5039,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="143" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="143" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B143" s="2" t="s">
         <v>32</v>
       </c>
@@ -5051,7 +5062,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="144" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="144" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B144" s="2"/>
       <c r="C144" s="3">
         <v>10822</v>
@@ -5072,7 +5083,7 @@
         <v>3999</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>37</v>
       </c>
@@ -5098,7 +5109,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B146" s="2" t="s">
         <v>7</v>
       </c>
@@ -5121,7 +5132,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B147" s="2" t="s">
         <v>8</v>
       </c>
@@ -5144,7 +5155,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B148" s="2" t="s">
         <v>9</v>
       </c>
@@ -5167,7 +5178,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B149" s="2" t="s">
         <v>10</v>
       </c>
@@ -5190,7 +5201,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B150" s="2" t="s">
         <v>11</v>
       </c>
@@ -5213,7 +5224,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B151" s="2" t="s">
         <v>12</v>
       </c>
@@ -5236,7 +5247,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B152" s="2" t="s">
         <v>13</v>
       </c>
@@ -5259,7 +5270,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B153" s="2" t="s">
         <v>14</v>
       </c>
@@ -5282,7 +5293,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B154" s="2" t="s">
         <v>15</v>
       </c>
@@ -5305,7 +5316,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B155" s="2" t="s">
         <v>16</v>
       </c>
@@ -5328,7 +5339,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B156" s="2" t="s">
         <v>17</v>
       </c>
@@ -5351,7 +5362,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B157" s="2" t="s">
         <v>18</v>
       </c>
@@ -5374,7 +5385,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B158" s="2" t="s">
         <v>19</v>
       </c>
@@ -5397,7 +5408,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B159" s="2" t="s">
         <v>20</v>
       </c>
@@ -5420,7 +5431,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B160" s="2" t="s">
         <v>21</v>
       </c>
@@ -5443,7 +5454,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B161" s="2" t="s">
         <v>22</v>
       </c>
@@ -5466,7 +5477,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B162" s="2" t="s">
         <v>23</v>
       </c>
@@ -5489,7 +5500,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B163" s="2" t="s">
         <v>24</v>
       </c>
@@ -5512,7 +5523,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B164" s="2" t="s">
         <v>25</v>
       </c>
@@ -5535,7 +5546,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B165" s="2" t="s">
         <v>26</v>
       </c>
@@ -5558,7 +5569,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B166" s="2" t="s">
         <v>27</v>
       </c>
@@ -5581,7 +5592,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B167" s="2" t="s">
         <v>28</v>
       </c>
@@ -5604,7 +5615,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B168" s="2" t="s">
         <v>29</v>
       </c>
@@ -5627,7 +5638,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B169" s="2" t="s">
         <v>30</v>
       </c>
@@ -5650,7 +5661,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B170" s="2" t="s">
         <v>31</v>
       </c>
@@ -5673,7 +5684,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B171" s="2" t="s">
         <v>32</v>
       </c>
@@ -5696,7 +5707,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C172" s="3">
         <v>5660</v>
       </c>
@@ -5716,7 +5727,7 @@
         <v>2598</v>
       </c>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>38</v>
       </c>
@@ -5729,7 +5740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>39</v>
       </c>
@@ -5742,242 +5753,242 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="203" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="204" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="205" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="206" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="207" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="208" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="209" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="210" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="211" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="212" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="213" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="214" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="215" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="216" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="218" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="219" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="221" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="222" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="223" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="224" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="225" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="226" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="232" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="234" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="235" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="237" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="238" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>62</v>
       </c>
@@ -5985,4 +5996,6346 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D27F840A-17F9-4FD0-8CBD-3F80D1850A12}">
+  <dimension ref="A1:AM170"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="31.42578125" customWidth="1"/>
+    <col min="3" max="3" width="15.28515625" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" customWidth="1"/>
+    <col min="6" max="6" width="13.140625" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:39" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:39" ht="30" x14ac:dyDescent="0.25">
+      <c r="C3" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" s="3">
+        <f>E40</f>
+        <v>-2319</v>
+      </c>
+      <c r="D4" s="3">
+        <f>F40</f>
+        <v>2436</v>
+      </c>
+      <c r="E4" s="3">
+        <f>G40</f>
+        <v>1762</v>
+      </c>
+      <c r="F4" s="3">
+        <f>H40</f>
+        <v>1879</v>
+      </c>
+      <c r="G4" s="4">
+        <v>28173</v>
+      </c>
+      <c r="H4" s="7">
+        <f>C4/$G4*100</f>
+        <v>-8.2312852731338513</v>
+      </c>
+      <c r="I4" s="7">
+        <f>D4/$G4*100</f>
+        <v>8.6465765094239178</v>
+      </c>
+      <c r="J4" s="7">
+        <f>E4/$G4*100</f>
+        <v>6.2542150285734568</v>
+      </c>
+      <c r="K4" s="7">
+        <f>F4/$G4*100</f>
+        <v>6.6695062648635215</v>
+      </c>
+    </row>
+    <row r="5" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" s="3">
+        <f>E66</f>
+        <v>-725</v>
+      </c>
+      <c r="D5" s="3">
+        <f t="shared" ref="D5:F5" si="0">F66</f>
+        <v>1774</v>
+      </c>
+      <c r="E5" s="3">
+        <f t="shared" si="0"/>
+        <v>4866</v>
+      </c>
+      <c r="F5" s="3">
+        <f t="shared" si="0"/>
+        <v>5915</v>
+      </c>
+      <c r="G5" s="4">
+        <v>27086</v>
+      </c>
+      <c r="H5" s="7">
+        <f t="shared" ref="H5:H10" si="1">C5/$G5*100</f>
+        <v>-2.6766595289079231</v>
+      </c>
+      <c r="I5" s="7">
+        <f t="shared" ref="I5:I10" si="2">D5/$G5*100</f>
+        <v>6.549508971424352</v>
+      </c>
+      <c r="J5" s="7">
+        <f t="shared" ref="J5:J10" si="3">E5/$G5*100</f>
+        <v>17.965000369194417</v>
+      </c>
+      <c r="K5" s="7">
+        <f t="shared" ref="K5:K10" si="4">F5/$G5*100</f>
+        <v>21.837849811710846</v>
+      </c>
+    </row>
+    <row r="6" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" s="3">
+        <f>E92</f>
+        <v>-1112</v>
+      </c>
+      <c r="D6" s="3">
+        <f>F92</f>
+        <v>4100</v>
+      </c>
+      <c r="E6" s="3">
+        <f>G92</f>
+        <v>5279</v>
+      </c>
+      <c r="F6" s="3">
+        <f>H92</f>
+        <v>8267</v>
+      </c>
+      <c r="G6" s="4">
+        <v>60246</v>
+      </c>
+      <c r="H6" s="7">
+        <f t="shared" si="1"/>
+        <v>-1.8457656939879825</v>
+      </c>
+      <c r="I6" s="7">
+        <f t="shared" si="2"/>
+        <v>6.8054310659628854</v>
+      </c>
+      <c r="J6" s="7">
+        <f t="shared" si="3"/>
+        <v>8.7624074627361157</v>
+      </c>
+      <c r="K6" s="7">
+        <f t="shared" si="4"/>
+        <v>13.722072834711019</v>
+      </c>
+    </row>
+    <row r="7" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" s="3">
+        <f>E118</f>
+        <v>-3416</v>
+      </c>
+      <c r="D7" s="3">
+        <f>F118</f>
+        <v>4971</v>
+      </c>
+      <c r="E7" s="3">
+        <f>G118</f>
+        <v>5889</v>
+      </c>
+      <c r="F7" s="3">
+        <f>H118</f>
+        <v>7444</v>
+      </c>
+      <c r="G7" s="4">
+        <v>67062</v>
+      </c>
+      <c r="H7" s="7">
+        <f t="shared" si="1"/>
+        <v>-5.0937938027496941</v>
+      </c>
+      <c r="I7" s="7">
+        <f t="shared" si="2"/>
+        <v>7.4125436163550145</v>
+      </c>
+      <c r="J7" s="7">
+        <f t="shared" si="3"/>
+        <v>8.7814261429721743</v>
+      </c>
+      <c r="K7" s="7">
+        <f t="shared" si="4"/>
+        <v>11.100175956577496</v>
+      </c>
+    </row>
+    <row r="8" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="3">
+        <f>E144</f>
+        <v>-4093</v>
+      </c>
+      <c r="D8" s="3">
+        <f>F144</f>
+        <v>2518</v>
+      </c>
+      <c r="E8" s="3">
+        <f>G144</f>
+        <v>5188</v>
+      </c>
+      <c r="F8" s="3">
+        <f>H144</f>
+        <v>3613</v>
+      </c>
+      <c r="G8" s="4">
+        <v>49022</v>
+      </c>
+      <c r="H8" s="7">
+        <f t="shared" si="1"/>
+        <v>-8.3493125535473869</v>
+      </c>
+      <c r="I8" s="7">
+        <f t="shared" si="2"/>
+        <v>5.1364693402961938</v>
+      </c>
+      <c r="J8" s="7">
+        <f t="shared" si="3"/>
+        <v>10.583003549426788</v>
+      </c>
+      <c r="K8" s="7">
+        <f t="shared" si="4"/>
+        <v>7.3701603361755952</v>
+      </c>
+    </row>
+    <row r="9" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="3">
+        <f>E170</f>
+        <v>-2996</v>
+      </c>
+      <c r="D9" s="3">
+        <f>F170</f>
+        <v>1827</v>
+      </c>
+      <c r="E9" s="3">
+        <f>G170</f>
+        <v>3524</v>
+      </c>
+      <c r="F9" s="3">
+        <f>H170</f>
+        <v>2355</v>
+      </c>
+      <c r="G9" s="4">
+        <v>27743</v>
+      </c>
+      <c r="H9" s="7">
+        <f t="shared" si="1"/>
+        <v>-10.799120498864578</v>
+      </c>
+      <c r="I9" s="7">
+        <f t="shared" si="2"/>
+        <v>6.5854449771113437</v>
+      </c>
+      <c r="J9" s="7">
+        <f t="shared" si="3"/>
+        <v>12.702303283711206</v>
+      </c>
+      <c r="K9" s="7">
+        <f t="shared" si="4"/>
+        <v>8.4886277619579715</v>
+      </c>
+    </row>
+    <row r="10" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" s="3">
+        <f>SUM(C4:C9)</f>
+        <v>-14661</v>
+      </c>
+      <c r="D10" s="3">
+        <f>SUM(D4:D9)</f>
+        <v>17626</v>
+      </c>
+      <c r="E10" s="3">
+        <f>SUM(E4:E9)</f>
+        <v>26508</v>
+      </c>
+      <c r="F10" s="3">
+        <f>SUM(F4:F9)</f>
+        <v>29473</v>
+      </c>
+      <c r="G10" s="3">
+        <f>SUM(G4:G9)</f>
+        <v>259332</v>
+      </c>
+      <c r="H10" s="7">
+        <f t="shared" si="1"/>
+        <v>-5.6533709684882698</v>
+      </c>
+      <c r="I10" s="7">
+        <f t="shared" si="2"/>
+        <v>6.7966930421236098</v>
+      </c>
+      <c r="J10" s="7">
+        <f t="shared" si="3"/>
+        <v>10.221646383786034</v>
+      </c>
+      <c r="K10" s="7">
+        <f t="shared" si="4"/>
+        <v>11.364968457421375</v>
+      </c>
+    </row>
+    <row r="13" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="C13" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="T13" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="X13" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AF13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ13" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="C14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="T14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="U14" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="V14" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="W14" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="X14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y14" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z14" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA14" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC14" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD14" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE14" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG14" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AH14" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI14" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK14" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AL14" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AM14" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="3">
+        <v>217</v>
+      </c>
+      <c r="D15" s="3">
+        <v>278</v>
+      </c>
+      <c r="E15" s="3">
+        <f>C15-D15</f>
+        <v>-61</v>
+      </c>
+      <c r="F15" s="3">
+        <v>110</v>
+      </c>
+      <c r="G15" s="3">
+        <v>20</v>
+      </c>
+      <c r="H15" s="3">
+        <f t="shared" ref="H15:H39" si="5">E15+F15+G15</f>
+        <v>69</v>
+      </c>
+      <c r="T15" s="3">
+        <v>255</v>
+      </c>
+      <c r="U15" s="3">
+        <v>238</v>
+      </c>
+      <c r="V15" s="3">
+        <v>70</v>
+      </c>
+      <c r="W15" s="3">
+        <v>71</v>
+      </c>
+      <c r="X15" s="3">
+        <v>555</v>
+      </c>
+      <c r="Y15" s="3">
+        <v>519</v>
+      </c>
+      <c r="Z15" s="3">
+        <v>214</v>
+      </c>
+      <c r="AA15" s="3">
+        <v>143</v>
+      </c>
+      <c r="AB15" s="3">
+        <v>556</v>
+      </c>
+      <c r="AC15" s="3">
+        <v>615</v>
+      </c>
+      <c r="AD15" s="3">
+        <v>171</v>
+      </c>
+      <c r="AE15" s="3">
+        <v>174</v>
+      </c>
+      <c r="AF15" s="3">
+        <v>385</v>
+      </c>
+      <c r="AG15" s="3">
+        <v>480</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>60</v>
+      </c>
+      <c r="AI15" s="3">
+        <v>110</v>
+      </c>
+      <c r="AJ15" s="3">
+        <v>197</v>
+      </c>
+      <c r="AK15" s="3">
+        <v>278</v>
+      </c>
+      <c r="AL15" s="3">
+        <v>94</v>
+      </c>
+      <c r="AM15" s="3">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="16" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="3">
+        <v>216</v>
+      </c>
+      <c r="D16" s="3">
+        <v>281</v>
+      </c>
+      <c r="E16" s="3">
+        <f t="shared" ref="E16:E81" si="6">C16-D16</f>
+        <v>-65</v>
+      </c>
+      <c r="F16" s="3">
+        <v>108</v>
+      </c>
+      <c r="G16" s="3">
+        <v>24</v>
+      </c>
+      <c r="H16" s="3">
+        <f t="shared" si="5"/>
+        <v>67</v>
+      </c>
+      <c r="T16" s="3">
+        <v>253</v>
+      </c>
+      <c r="U16" s="3">
+        <v>241</v>
+      </c>
+      <c r="V16" s="3">
+        <v>72</v>
+      </c>
+      <c r="W16" s="3">
+        <v>104</v>
+      </c>
+      <c r="X16" s="3">
+        <v>554</v>
+      </c>
+      <c r="Y16" s="3">
+        <v>524</v>
+      </c>
+      <c r="Z16" s="3">
+        <v>206</v>
+      </c>
+      <c r="AA16" s="3">
+        <v>164</v>
+      </c>
+      <c r="AB16" s="3">
+        <v>556</v>
+      </c>
+      <c r="AC16" s="3">
+        <v>619</v>
+      </c>
+      <c r="AD16" s="3">
+        <v>181</v>
+      </c>
+      <c r="AE16" s="3">
+        <v>191</v>
+      </c>
+      <c r="AF16" s="3">
+        <v>387</v>
+      </c>
+      <c r="AG16" s="3">
+        <v>485</v>
+      </c>
+      <c r="AH16" s="3">
+        <v>72</v>
+      </c>
+      <c r="AI16" s="3">
+        <v>126</v>
+      </c>
+      <c r="AJ16" s="3">
+        <v>199</v>
+      </c>
+      <c r="AK16" s="3">
+        <v>281</v>
+      </c>
+      <c r="AL16" s="3">
+        <v>90</v>
+      </c>
+      <c r="AM16" s="3">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="17" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="3">
+        <v>217</v>
+      </c>
+      <c r="D17" s="3">
+        <v>284</v>
+      </c>
+      <c r="E17" s="3">
+        <f t="shared" si="6"/>
+        <v>-67</v>
+      </c>
+      <c r="F17" s="3">
+        <v>107</v>
+      </c>
+      <c r="G17" s="3">
+        <v>27</v>
+      </c>
+      <c r="H17" s="3">
+        <f t="shared" si="5"/>
+        <v>67</v>
+      </c>
+      <c r="T17" s="3">
+        <v>253</v>
+      </c>
+      <c r="U17" s="3">
+        <v>246</v>
+      </c>
+      <c r="V17" s="3">
+        <v>76</v>
+      </c>
+      <c r="W17" s="3">
+        <v>136</v>
+      </c>
+      <c r="X17" s="3">
+        <v>556</v>
+      </c>
+      <c r="Y17" s="3">
+        <v>528</v>
+      </c>
+      <c r="Z17" s="3">
+        <v>197</v>
+      </c>
+      <c r="AA17" s="3">
+        <v>181</v>
+      </c>
+      <c r="AB17" s="3">
+        <v>558</v>
+      </c>
+      <c r="AC17" s="3">
+        <v>626</v>
+      </c>
+      <c r="AD17" s="3">
+        <v>192</v>
+      </c>
+      <c r="AE17" s="3">
+        <v>206</v>
+      </c>
+      <c r="AF17" s="3">
+        <v>389</v>
+      </c>
+      <c r="AG17" s="3">
+        <v>489</v>
+      </c>
+      <c r="AH17" s="3">
+        <v>83</v>
+      </c>
+      <c r="AI17" s="3">
+        <v>141</v>
+      </c>
+      <c r="AJ17" s="3">
+        <v>199</v>
+      </c>
+      <c r="AK17" s="3">
+        <v>282</v>
+      </c>
+      <c r="AL17" s="3">
+        <v>86</v>
+      </c>
+      <c r="AM17" s="3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="18" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="3">
+        <v>218</v>
+      </c>
+      <c r="D18" s="3">
+        <v>287</v>
+      </c>
+      <c r="E18" s="3">
+        <f t="shared" si="6"/>
+        <v>-69</v>
+      </c>
+      <c r="F18" s="3">
+        <v>105</v>
+      </c>
+      <c r="G18" s="3">
+        <v>34</v>
+      </c>
+      <c r="H18" s="3">
+        <f t="shared" si="5"/>
+        <v>70</v>
+      </c>
+      <c r="T18" s="3">
+        <v>255</v>
+      </c>
+      <c r="U18" s="3">
+        <v>251</v>
+      </c>
+      <c r="V18" s="3">
+        <v>76</v>
+      </c>
+      <c r="W18" s="3">
+        <v>168</v>
+      </c>
+      <c r="X18" s="3">
+        <v>556</v>
+      </c>
+      <c r="Y18" s="3">
+        <v>536</v>
+      </c>
+      <c r="Z18" s="3">
+        <v>190</v>
+      </c>
+      <c r="AA18" s="3">
+        <v>197</v>
+      </c>
+      <c r="AB18" s="3">
+        <v>560</v>
+      </c>
+      <c r="AC18" s="3">
+        <v>634</v>
+      </c>
+      <c r="AD18" s="3">
+        <v>203</v>
+      </c>
+      <c r="AE18" s="3">
+        <v>218</v>
+      </c>
+      <c r="AF18" s="3">
+        <v>393</v>
+      </c>
+      <c r="AG18" s="3">
+        <v>496</v>
+      </c>
+      <c r="AH18" s="3">
+        <v>94</v>
+      </c>
+      <c r="AI18" s="3">
+        <v>156</v>
+      </c>
+      <c r="AJ18" s="3">
+        <v>201</v>
+      </c>
+      <c r="AK18" s="3">
+        <v>286</v>
+      </c>
+      <c r="AL18" s="3">
+        <v>82</v>
+      </c>
+      <c r="AM18" s="3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="19" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="3">
+        <v>219</v>
+      </c>
+      <c r="D19" s="3">
+        <v>291</v>
+      </c>
+      <c r="E19" s="3">
+        <f t="shared" si="6"/>
+        <v>-72</v>
+      </c>
+      <c r="F19" s="3">
+        <v>103</v>
+      </c>
+      <c r="G19" s="3">
+        <v>41</v>
+      </c>
+      <c r="H19" s="3">
+        <f t="shared" si="5"/>
+        <v>72</v>
+      </c>
+      <c r="T19" s="3">
+        <v>257</v>
+      </c>
+      <c r="U19" s="3">
+        <v>256</v>
+      </c>
+      <c r="V19" s="3">
+        <v>79</v>
+      </c>
+      <c r="W19" s="3">
+        <v>197</v>
+      </c>
+      <c r="X19" s="3">
+        <v>559</v>
+      </c>
+      <c r="Y19" s="3">
+        <v>543</v>
+      </c>
+      <c r="Z19" s="3">
+        <v>180</v>
+      </c>
+      <c r="AA19" s="3">
+        <v>212</v>
+      </c>
+      <c r="AB19" s="3">
+        <v>562</v>
+      </c>
+      <c r="AC19" s="3">
+        <v>643</v>
+      </c>
+      <c r="AD19" s="3">
+        <v>210</v>
+      </c>
+      <c r="AE19" s="3">
+        <v>228</v>
+      </c>
+      <c r="AF19" s="3">
+        <v>395</v>
+      </c>
+      <c r="AG19" s="3">
+        <v>504</v>
+      </c>
+      <c r="AH19" s="3">
+        <v>104</v>
+      </c>
+      <c r="AI19" s="3">
+        <v>172</v>
+      </c>
+      <c r="AJ19" s="3">
+        <v>202</v>
+      </c>
+      <c r="AK19" s="3">
+        <v>290</v>
+      </c>
+      <c r="AL19" s="3">
+        <v>79</v>
+      </c>
+      <c r="AM19" s="3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="20" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="3">
+        <v>221</v>
+      </c>
+      <c r="D20" s="3">
+        <v>295</v>
+      </c>
+      <c r="E20" s="3">
+        <f t="shared" si="6"/>
+        <v>-74</v>
+      </c>
+      <c r="F20" s="3">
+        <v>100</v>
+      </c>
+      <c r="G20" s="3">
+        <v>49</v>
+      </c>
+      <c r="H20" s="3">
+        <f t="shared" si="5"/>
+        <v>75</v>
+      </c>
+      <c r="T20" s="3">
+        <v>259</v>
+      </c>
+      <c r="U20" s="3">
+        <v>262</v>
+      </c>
+      <c r="V20" s="3">
+        <v>79</v>
+      </c>
+      <c r="W20" s="3">
+        <v>228</v>
+      </c>
+      <c r="X20" s="3">
+        <v>562</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>551</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>169</v>
+      </c>
+      <c r="AA20" s="3">
+        <v>227</v>
+      </c>
+      <c r="AB20" s="3">
+        <v>567</v>
+      </c>
+      <c r="AC20" s="3">
+        <v>651</v>
+      </c>
+      <c r="AD20" s="3">
+        <v>215</v>
+      </c>
+      <c r="AE20" s="3">
+        <v>235</v>
+      </c>
+      <c r="AF20" s="3">
+        <v>399</v>
+      </c>
+      <c r="AG20" s="3">
+        <v>511</v>
+      </c>
+      <c r="AH20" s="3">
+        <v>112</v>
+      </c>
+      <c r="AI20" s="3">
+        <v>186</v>
+      </c>
+      <c r="AJ20" s="3">
+        <v>205</v>
+      </c>
+      <c r="AK20" s="3">
+        <v>295</v>
+      </c>
+      <c r="AL20" s="3">
+        <v>74</v>
+      </c>
+      <c r="AM20" s="3">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="21" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" s="3">
+        <v>224</v>
+      </c>
+      <c r="D21" s="3">
+        <v>300</v>
+      </c>
+      <c r="E21" s="3">
+        <f t="shared" si="6"/>
+        <v>-76</v>
+      </c>
+      <c r="F21" s="3">
+        <v>100</v>
+      </c>
+      <c r="G21" s="3">
+        <v>53</v>
+      </c>
+      <c r="H21" s="3">
+        <f t="shared" si="5"/>
+        <v>77</v>
+      </c>
+      <c r="T21" s="3">
+        <v>264</v>
+      </c>
+      <c r="U21" s="3">
+        <v>268</v>
+      </c>
+      <c r="V21" s="3">
+        <v>78</v>
+      </c>
+      <c r="W21" s="3">
+        <v>224</v>
+      </c>
+      <c r="X21" s="3">
+        <v>566</v>
+      </c>
+      <c r="Y21" s="3">
+        <v>559</v>
+      </c>
+      <c r="Z21" s="3">
+        <v>167</v>
+      </c>
+      <c r="AA21" s="3">
+        <v>224</v>
+      </c>
+      <c r="AB21" s="3">
+        <v>572</v>
+      </c>
+      <c r="AC21" s="3">
+        <v>662</v>
+      </c>
+      <c r="AD21" s="3">
+        <v>213</v>
+      </c>
+      <c r="AE21" s="3">
+        <v>233</v>
+      </c>
+      <c r="AF21" s="3">
+        <v>403</v>
+      </c>
+      <c r="AG21" s="3">
+        <v>519</v>
+      </c>
+      <c r="AH21" s="3">
+        <v>111</v>
+      </c>
+      <c r="AI21" s="3">
+        <v>193</v>
+      </c>
+      <c r="AJ21" s="3">
+        <v>205</v>
+      </c>
+      <c r="AK21" s="3">
+        <v>299</v>
+      </c>
+      <c r="AL21" s="3">
+        <v>73</v>
+      </c>
+      <c r="AM21" s="3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="22" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="3">
+        <v>228</v>
+      </c>
+      <c r="D22" s="3">
+        <v>304</v>
+      </c>
+      <c r="E22" s="3">
+        <f t="shared" si="6"/>
+        <v>-76</v>
+      </c>
+      <c r="F22" s="3">
+        <v>100</v>
+      </c>
+      <c r="G22" s="3">
+        <v>55</v>
+      </c>
+      <c r="H22" s="3">
+        <f t="shared" si="5"/>
+        <v>79</v>
+      </c>
+      <c r="T22" s="3">
+        <v>267</v>
+      </c>
+      <c r="U22" s="3">
+        <v>274</v>
+      </c>
+      <c r="V22" s="3">
+        <v>77</v>
+      </c>
+      <c r="W22" s="3">
+        <v>222</v>
+      </c>
+      <c r="X22" s="3">
+        <v>572</v>
+      </c>
+      <c r="Y22" s="3">
+        <v>570</v>
+      </c>
+      <c r="Z22" s="3">
+        <v>168</v>
+      </c>
+      <c r="AA22" s="3">
+        <v>221</v>
+      </c>
+      <c r="AB22" s="3">
+        <v>578</v>
+      </c>
+      <c r="AC22" s="3">
+        <v>673</v>
+      </c>
+      <c r="AD22" s="3">
+        <v>215</v>
+      </c>
+      <c r="AE22" s="3">
+        <v>232</v>
+      </c>
+      <c r="AF22" s="3">
+        <v>407</v>
+      </c>
+      <c r="AG22" s="3">
+        <v>528</v>
+      </c>
+      <c r="AH22" s="3">
+        <v>112</v>
+      </c>
+      <c r="AI22" s="3">
+        <v>197</v>
+      </c>
+      <c r="AJ22" s="3">
+        <v>209</v>
+      </c>
+      <c r="AK22" s="3">
+        <v>305</v>
+      </c>
+      <c r="AL22" s="3">
+        <v>74</v>
+      </c>
+      <c r="AM22" s="3">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="23" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" s="3">
+        <v>230</v>
+      </c>
+      <c r="D23" s="3">
+        <v>308</v>
+      </c>
+      <c r="E23" s="3">
+        <f t="shared" si="6"/>
+        <v>-78</v>
+      </c>
+      <c r="F23" s="3">
+        <v>100</v>
+      </c>
+      <c r="G23" s="3">
+        <v>60</v>
+      </c>
+      <c r="H23" s="3">
+        <f t="shared" si="5"/>
+        <v>82</v>
+      </c>
+      <c r="T23" s="3">
+        <v>271</v>
+      </c>
+      <c r="U23" s="3">
+        <v>280</v>
+      </c>
+      <c r="V23" s="3">
+        <v>77</v>
+      </c>
+      <c r="W23" s="3">
+        <v>219</v>
+      </c>
+      <c r="X23" s="3">
+        <v>576</v>
+      </c>
+      <c r="Y23" s="3">
+        <v>579</v>
+      </c>
+      <c r="Z23" s="3">
+        <v>168</v>
+      </c>
+      <c r="AA23" s="3">
+        <v>221</v>
+      </c>
+      <c r="AB23" s="3">
+        <v>584</v>
+      </c>
+      <c r="AC23" s="3">
+        <v>682</v>
+      </c>
+      <c r="AD23" s="3">
+        <v>215</v>
+      </c>
+      <c r="AE23" s="3">
+        <v>230</v>
+      </c>
+      <c r="AF23" s="3">
+        <v>411</v>
+      </c>
+      <c r="AG23" s="3">
+        <v>537</v>
+      </c>
+      <c r="AH23" s="3">
+        <v>112</v>
+      </c>
+      <c r="AI23" s="3">
+        <v>201</v>
+      </c>
+      <c r="AJ23" s="3">
+        <v>210</v>
+      </c>
+      <c r="AK23" s="3">
+        <v>310</v>
+      </c>
+      <c r="AL23" s="3">
+        <v>74</v>
+      </c>
+      <c r="AM23" s="3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="24" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" s="3">
+        <v>233</v>
+      </c>
+      <c r="D24" s="3">
+        <v>312</v>
+      </c>
+      <c r="E24" s="3">
+        <f t="shared" si="6"/>
+        <v>-79</v>
+      </c>
+      <c r="F24" s="3">
+        <v>100</v>
+      </c>
+      <c r="G24" s="3">
+        <v>64</v>
+      </c>
+      <c r="H24" s="3">
+        <f t="shared" si="5"/>
+        <v>85</v>
+      </c>
+      <c r="T24" s="3">
+        <v>276</v>
+      </c>
+      <c r="U24" s="3">
+        <v>286</v>
+      </c>
+      <c r="V24" s="3">
+        <v>76</v>
+      </c>
+      <c r="W24" s="3">
+        <v>217</v>
+      </c>
+      <c r="X24" s="3">
+        <v>583</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>589</v>
+      </c>
+      <c r="Z24" s="3">
+        <v>166</v>
+      </c>
+      <c r="AA24" s="3">
+        <v>221</v>
+      </c>
+      <c r="AB24" s="3">
+        <v>592</v>
+      </c>
+      <c r="AC24" s="3">
+        <v>693</v>
+      </c>
+      <c r="AD24" s="3">
+        <v>213</v>
+      </c>
+      <c r="AE24" s="3">
+        <v>230</v>
+      </c>
+      <c r="AF24" s="3">
+        <v>414</v>
+      </c>
+      <c r="AG24" s="3">
+        <v>545</v>
+      </c>
+      <c r="AH24" s="3">
+        <v>111</v>
+      </c>
+      <c r="AI24" s="3">
+        <v>205</v>
+      </c>
+      <c r="AJ24" s="3">
+        <v>212</v>
+      </c>
+      <c r="AK24" s="3">
+        <v>315</v>
+      </c>
+      <c r="AL24" s="3">
+        <v>74</v>
+      </c>
+      <c r="AM24" s="3">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="25" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="3">
+        <v>234</v>
+      </c>
+      <c r="D25" s="3">
+        <v>317</v>
+      </c>
+      <c r="E25" s="3">
+        <f t="shared" si="6"/>
+        <v>-83</v>
+      </c>
+      <c r="F25" s="3">
+        <v>99</v>
+      </c>
+      <c r="G25" s="3">
+        <v>69</v>
+      </c>
+      <c r="H25" s="3">
+        <f t="shared" si="5"/>
+        <v>85</v>
+      </c>
+      <c r="T25" s="3">
+        <v>277</v>
+      </c>
+      <c r="U25" s="3">
+        <v>292</v>
+      </c>
+      <c r="V25" s="3">
+        <v>75</v>
+      </c>
+      <c r="W25" s="3">
+        <v>216</v>
+      </c>
+      <c r="X25" s="3">
+        <v>584</v>
+      </c>
+      <c r="Y25" s="3">
+        <v>599</v>
+      </c>
+      <c r="Z25" s="3">
+        <v>165</v>
+      </c>
+      <c r="AA25" s="3">
+        <v>220</v>
+      </c>
+      <c r="AB25" s="3">
+        <v>593</v>
+      </c>
+      <c r="AC25" s="3">
+        <v>704</v>
+      </c>
+      <c r="AD25" s="3">
+        <v>212</v>
+      </c>
+      <c r="AE25" s="3">
+        <v>230</v>
+      </c>
+      <c r="AF25" s="3">
+        <v>414</v>
+      </c>
+      <c r="AG25" s="3">
+        <v>556</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>111</v>
+      </c>
+      <c r="AI25" s="3">
+        <v>209</v>
+      </c>
+      <c r="AJ25" s="3">
+        <v>213</v>
+      </c>
+      <c r="AK25" s="3">
+        <v>321</v>
+      </c>
+      <c r="AL25" s="3">
+        <v>74</v>
+      </c>
+      <c r="AM25" s="3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="26" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26" s="3">
+        <v>234</v>
+      </c>
+      <c r="D26" s="3">
+        <v>321</v>
+      </c>
+      <c r="E26" s="3">
+        <f t="shared" si="6"/>
+        <v>-87</v>
+      </c>
+      <c r="F26" s="3">
+        <v>99</v>
+      </c>
+      <c r="G26" s="3">
+        <v>74</v>
+      </c>
+      <c r="H26" s="3">
+        <f t="shared" si="5"/>
+        <v>86</v>
+      </c>
+      <c r="T26" s="3">
+        <v>277</v>
+      </c>
+      <c r="U26" s="3">
+        <v>298</v>
+      </c>
+      <c r="V26" s="3">
+        <v>74</v>
+      </c>
+      <c r="W26" s="3">
+        <v>215</v>
+      </c>
+      <c r="X26" s="3">
+        <v>585</v>
+      </c>
+      <c r="Y26" s="3">
+        <v>609</v>
+      </c>
+      <c r="Z26" s="3">
+        <v>163</v>
+      </c>
+      <c r="AA26" s="3">
+        <v>220</v>
+      </c>
+      <c r="AB26" s="3">
+        <v>594</v>
+      </c>
+      <c r="AC26" s="3">
+        <v>713</v>
+      </c>
+      <c r="AD26" s="3">
+        <v>210</v>
+      </c>
+      <c r="AE26" s="3">
+        <v>232</v>
+      </c>
+      <c r="AF26" s="3">
+        <v>413</v>
+      </c>
+      <c r="AG26" s="3">
+        <v>564</v>
+      </c>
+      <c r="AH26" s="3">
+        <v>110</v>
+      </c>
+      <c r="AI26" s="3">
+        <v>212</v>
+      </c>
+      <c r="AJ26" s="3">
+        <v>213</v>
+      </c>
+      <c r="AK26" s="3">
+        <v>325</v>
+      </c>
+      <c r="AL26" s="3">
+        <v>72</v>
+      </c>
+      <c r="AM26" s="3">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="27" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C27" s="3">
+        <v>235</v>
+      </c>
+      <c r="D27" s="3">
+        <v>324</v>
+      </c>
+      <c r="E27" s="3">
+        <f t="shared" si="6"/>
+        <v>-89</v>
+      </c>
+      <c r="F27" s="3">
+        <v>97</v>
+      </c>
+      <c r="G27" s="3">
+        <v>78</v>
+      </c>
+      <c r="H27" s="3">
+        <f t="shared" si="5"/>
+        <v>86</v>
+      </c>
+      <c r="T27" s="3">
+        <v>278</v>
+      </c>
+      <c r="U27" s="3">
+        <v>303</v>
+      </c>
+      <c r="V27" s="3">
+        <v>73</v>
+      </c>
+      <c r="W27" s="3">
+        <v>214</v>
+      </c>
+      <c r="X27" s="3">
+        <v>586</v>
+      </c>
+      <c r="Y27" s="3">
+        <v>619</v>
+      </c>
+      <c r="Z27" s="3">
+        <v>161</v>
+      </c>
+      <c r="AA27" s="3">
+        <v>220</v>
+      </c>
+      <c r="AB27" s="3">
+        <v>595</v>
+      </c>
+      <c r="AC27" s="3">
+        <v>724</v>
+      </c>
+      <c r="AD27" s="3">
+        <v>208</v>
+      </c>
+      <c r="AE27" s="3">
+        <v>235</v>
+      </c>
+      <c r="AF27" s="3">
+        <v>412</v>
+      </c>
+      <c r="AG27" s="3">
+        <v>572</v>
+      </c>
+      <c r="AH27" s="3">
+        <v>108</v>
+      </c>
+      <c r="AI27" s="3">
+        <v>217</v>
+      </c>
+      <c r="AJ27" s="3">
+        <v>213</v>
+      </c>
+      <c r="AK27" s="3">
+        <v>331</v>
+      </c>
+      <c r="AL27" s="3">
+        <v>72</v>
+      </c>
+      <c r="AM27" s="3">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="28" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C28" s="3">
+        <v>234</v>
+      </c>
+      <c r="D28" s="3">
+        <v>328</v>
+      </c>
+      <c r="E28" s="3">
+        <f t="shared" si="6"/>
+        <v>-94</v>
+      </c>
+      <c r="F28" s="3">
+        <v>98</v>
+      </c>
+      <c r="G28" s="3">
+        <v>81</v>
+      </c>
+      <c r="H28" s="3">
+        <f t="shared" si="5"/>
+        <v>85</v>
+      </c>
+      <c r="T28" s="3">
+        <v>278</v>
+      </c>
+      <c r="U28" s="3">
+        <v>308</v>
+      </c>
+      <c r="V28" s="3">
+        <v>72</v>
+      </c>
+      <c r="W28" s="3">
+        <v>213</v>
+      </c>
+      <c r="X28" s="3">
+        <v>585</v>
+      </c>
+      <c r="Y28" s="3">
+        <v>628</v>
+      </c>
+      <c r="Z28" s="3">
+        <v>160</v>
+      </c>
+      <c r="AA28" s="3">
+        <v>219</v>
+      </c>
+      <c r="AB28" s="3">
+        <v>596</v>
+      </c>
+      <c r="AC28" s="3">
+        <v>731</v>
+      </c>
+      <c r="AD28" s="3">
+        <v>206</v>
+      </c>
+      <c r="AE28" s="3">
+        <v>238</v>
+      </c>
+      <c r="AF28" s="3">
+        <v>412</v>
+      </c>
+      <c r="AG28" s="3">
+        <v>581</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>108</v>
+      </c>
+      <c r="AI28" s="3">
+        <v>220</v>
+      </c>
+      <c r="AJ28" s="3">
+        <v>213</v>
+      </c>
+      <c r="AK28" s="3">
+        <v>336</v>
+      </c>
+      <c r="AL28" s="3">
+        <v>72</v>
+      </c>
+      <c r="AM28" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="29" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C29" s="3">
+        <v>233</v>
+      </c>
+      <c r="D29" s="3">
+        <v>330</v>
+      </c>
+      <c r="E29" s="3">
+        <f t="shared" si="6"/>
+        <v>-97</v>
+      </c>
+      <c r="F29" s="3">
+        <v>96</v>
+      </c>
+      <c r="G29" s="3">
+        <v>85</v>
+      </c>
+      <c r="H29" s="3">
+        <f t="shared" si="5"/>
+        <v>84</v>
+      </c>
+      <c r="T29" s="3">
+        <v>279</v>
+      </c>
+      <c r="U29" s="3">
+        <v>313</v>
+      </c>
+      <c r="V29" s="3">
+        <v>70</v>
+      </c>
+      <c r="W29" s="3">
+        <v>212</v>
+      </c>
+      <c r="X29" s="3">
+        <v>586</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>637</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>157</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>218</v>
+      </c>
+      <c r="AB29" s="3">
+        <v>594</v>
+      </c>
+      <c r="AC29" s="3">
+        <v>740</v>
+      </c>
+      <c r="AD29" s="3">
+        <v>204</v>
+      </c>
+      <c r="AE29" s="3">
+        <v>244</v>
+      </c>
+      <c r="AF29" s="3">
+        <v>410</v>
+      </c>
+      <c r="AG29" s="3">
+        <v>589</v>
+      </c>
+      <c r="AH29" s="3">
+        <v>107</v>
+      </c>
+      <c r="AI29" s="3">
+        <v>227</v>
+      </c>
+      <c r="AJ29" s="3">
+        <v>213</v>
+      </c>
+      <c r="AK29" s="3">
+        <v>339</v>
+      </c>
+      <c r="AL29" s="3">
+        <v>70</v>
+      </c>
+      <c r="AM29" s="3">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="30" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C30" s="3">
+        <v>233</v>
+      </c>
+      <c r="D30" s="3">
+        <v>333</v>
+      </c>
+      <c r="E30" s="3">
+        <f t="shared" si="6"/>
+        <v>-100</v>
+      </c>
+      <c r="F30" s="3">
+        <v>96</v>
+      </c>
+      <c r="G30" s="3">
+        <v>87</v>
+      </c>
+      <c r="H30" s="3">
+        <f t="shared" si="5"/>
+        <v>83</v>
+      </c>
+      <c r="T30" s="3">
+        <v>278</v>
+      </c>
+      <c r="U30" s="3">
+        <v>317</v>
+      </c>
+      <c r="V30" s="3">
+        <v>70</v>
+      </c>
+      <c r="W30" s="3">
+        <v>210</v>
+      </c>
+      <c r="X30" s="3">
+        <v>584</v>
+      </c>
+      <c r="Y30" s="3">
+        <v>645</v>
+      </c>
+      <c r="Z30" s="3">
+        <v>155</v>
+      </c>
+      <c r="AA30" s="3">
+        <v>220</v>
+      </c>
+      <c r="AB30" s="3">
+        <v>593</v>
+      </c>
+      <c r="AC30" s="3">
+        <v>746</v>
+      </c>
+      <c r="AD30" s="3">
+        <v>201</v>
+      </c>
+      <c r="AE30" s="3">
+        <v>247</v>
+      </c>
+      <c r="AF30" s="3">
+        <v>409</v>
+      </c>
+      <c r="AG30" s="3">
+        <v>595</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>105</v>
+      </c>
+      <c r="AI30" s="3">
+        <v>231</v>
+      </c>
+      <c r="AJ30" s="3">
+        <v>213</v>
+      </c>
+      <c r="AK30" s="3">
+        <v>344</v>
+      </c>
+      <c r="AL30" s="3">
+        <v>70</v>
+      </c>
+      <c r="AM30" s="3">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="31" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C31" s="3">
+        <v>232</v>
+      </c>
+      <c r="D31" s="3">
+        <v>335</v>
+      </c>
+      <c r="E31" s="3">
+        <f t="shared" si="6"/>
+        <v>-103</v>
+      </c>
+      <c r="F31" s="3">
+        <v>94</v>
+      </c>
+      <c r="G31" s="3">
+        <v>90</v>
+      </c>
+      <c r="H31" s="3">
+        <f t="shared" si="5"/>
+        <v>81</v>
+      </c>
+      <c r="T31" s="3">
+        <v>278</v>
+      </c>
+      <c r="U31" s="3">
+        <v>322</v>
+      </c>
+      <c r="V31" s="3">
+        <v>69</v>
+      </c>
+      <c r="W31" s="3">
+        <v>209</v>
+      </c>
+      <c r="X31" s="3">
+        <v>583</v>
+      </c>
+      <c r="Y31" s="3">
+        <v>654</v>
+      </c>
+      <c r="Z31" s="3">
+        <v>154</v>
+      </c>
+      <c r="AA31" s="3">
+        <v>219</v>
+      </c>
+      <c r="AB31" s="3">
+        <v>591</v>
+      </c>
+      <c r="AC31" s="3">
+        <v>754</v>
+      </c>
+      <c r="AD31" s="3">
+        <v>200</v>
+      </c>
+      <c r="AE31" s="3">
+        <v>252</v>
+      </c>
+      <c r="AF31" s="3">
+        <v>406</v>
+      </c>
+      <c r="AG31" s="3">
+        <v>601</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>105</v>
+      </c>
+      <c r="AI31" s="3">
+        <v>236</v>
+      </c>
+      <c r="AJ31" s="3">
+        <v>211</v>
+      </c>
+      <c r="AK31" s="3">
+        <v>347</v>
+      </c>
+      <c r="AL31" s="3">
+        <v>70</v>
+      </c>
+      <c r="AM31" s="3">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="32" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C32" s="3">
+        <v>230</v>
+      </c>
+      <c r="D32" s="3">
+        <v>337</v>
+      </c>
+      <c r="E32" s="3">
+        <f t="shared" si="6"/>
+        <v>-107</v>
+      </c>
+      <c r="F32" s="3">
+        <v>94</v>
+      </c>
+      <c r="G32" s="3">
+        <v>92</v>
+      </c>
+      <c r="H32" s="3">
+        <f t="shared" si="5"/>
+        <v>79</v>
+      </c>
+      <c r="T32" s="3">
+        <v>276</v>
+      </c>
+      <c r="U32" s="3">
+        <v>325</v>
+      </c>
+      <c r="V32" s="3">
+        <v>67</v>
+      </c>
+      <c r="W32" s="3">
+        <v>207</v>
+      </c>
+      <c r="X32" s="3">
+        <v>580</v>
+      </c>
+      <c r="Y32" s="3">
+        <v>661</v>
+      </c>
+      <c r="Z32" s="3">
+        <v>152</v>
+      </c>
+      <c r="AA32" s="3">
+        <v>219</v>
+      </c>
+      <c r="AB32" s="3">
+        <v>588</v>
+      </c>
+      <c r="AC32" s="3">
+        <v>759</v>
+      </c>
+      <c r="AD32" s="3">
+        <v>196</v>
+      </c>
+      <c r="AE32" s="3">
+        <v>254</v>
+      </c>
+      <c r="AF32" s="3">
+        <v>404</v>
+      </c>
+      <c r="AG32" s="3">
+        <v>606</v>
+      </c>
+      <c r="AH32" s="3">
+        <v>103</v>
+      </c>
+      <c r="AI32" s="3">
+        <v>240</v>
+      </c>
+      <c r="AJ32" s="3">
+        <v>211</v>
+      </c>
+      <c r="AK32" s="3">
+        <v>351</v>
+      </c>
+      <c r="AL32" s="3">
+        <v>68</v>
+      </c>
+      <c r="AM32" s="3">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="33" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C33" s="3">
+        <v>229</v>
+      </c>
+      <c r="D33" s="3">
+        <v>338</v>
+      </c>
+      <c r="E33" s="3">
+        <f t="shared" si="6"/>
+        <v>-109</v>
+      </c>
+      <c r="F33" s="3">
+        <v>93</v>
+      </c>
+      <c r="G33" s="3">
+        <v>93</v>
+      </c>
+      <c r="H33" s="3">
+        <f t="shared" si="5"/>
+        <v>77</v>
+      </c>
+      <c r="T33" s="3">
+        <v>275</v>
+      </c>
+      <c r="U33" s="3">
+        <v>328</v>
+      </c>
+      <c r="V33" s="3">
+        <v>66</v>
+      </c>
+      <c r="W33" s="3">
+        <v>206</v>
+      </c>
+      <c r="X33" s="3">
+        <v>577</v>
+      </c>
+      <c r="Y33" s="3">
+        <v>668</v>
+      </c>
+      <c r="Z33" s="3">
+        <v>149</v>
+      </c>
+      <c r="AA33" s="3">
+        <v>217</v>
+      </c>
+      <c r="AB33" s="3">
+        <v>584</v>
+      </c>
+      <c r="AC33" s="3">
+        <v>765</v>
+      </c>
+      <c r="AD33" s="3">
+        <v>195</v>
+      </c>
+      <c r="AE33" s="3">
+        <v>255</v>
+      </c>
+      <c r="AF33" s="3">
+        <v>401</v>
+      </c>
+      <c r="AG33" s="3">
+        <v>611</v>
+      </c>
+      <c r="AH33" s="3">
+        <v>102</v>
+      </c>
+      <c r="AI33" s="3">
+        <v>243</v>
+      </c>
+      <c r="AJ33" s="3">
+        <v>209</v>
+      </c>
+      <c r="AK33" s="3">
+        <v>354</v>
+      </c>
+      <c r="AL33" s="3">
+        <v>68</v>
+      </c>
+      <c r="AM33" s="3">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="34" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C34" s="3">
+        <v>227</v>
+      </c>
+      <c r="D34" s="3">
+        <v>340</v>
+      </c>
+      <c r="E34" s="3">
+        <f t="shared" si="6"/>
+        <v>-113</v>
+      </c>
+      <c r="F34" s="3">
+        <v>92</v>
+      </c>
+      <c r="G34" s="3">
+        <v>95</v>
+      </c>
+      <c r="H34" s="3">
+        <f t="shared" si="5"/>
+        <v>74</v>
+      </c>
+      <c r="T34" s="3">
+        <v>273</v>
+      </c>
+      <c r="U34" s="3">
+        <v>332</v>
+      </c>
+      <c r="V34" s="3">
+        <v>66</v>
+      </c>
+      <c r="W34" s="3">
+        <v>203</v>
+      </c>
+      <c r="X34" s="3">
+        <v>573</v>
+      </c>
+      <c r="Y34" s="3">
+        <v>676</v>
+      </c>
+      <c r="Z34" s="3">
+        <v>148</v>
+      </c>
+      <c r="AA34" s="3">
+        <v>217</v>
+      </c>
+      <c r="AB34" s="3">
+        <v>581</v>
+      </c>
+      <c r="AC34" s="3">
+        <v>771</v>
+      </c>
+      <c r="AD34" s="3">
+        <v>192</v>
+      </c>
+      <c r="AE34" s="3">
+        <v>256</v>
+      </c>
+      <c r="AF34" s="3">
+        <v>398</v>
+      </c>
+      <c r="AG34" s="3">
+        <v>614</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>101</v>
+      </c>
+      <c r="AI34" s="3">
+        <v>245</v>
+      </c>
+      <c r="AJ34" s="3">
+        <v>209</v>
+      </c>
+      <c r="AK34" s="3">
+        <v>357</v>
+      </c>
+      <c r="AL34" s="3">
+        <v>67</v>
+      </c>
+      <c r="AM34" s="3">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="35" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C35" s="3">
+        <v>225</v>
+      </c>
+      <c r="D35" s="3">
+        <v>343</v>
+      </c>
+      <c r="E35" s="3">
+        <f t="shared" si="6"/>
+        <v>-118</v>
+      </c>
+      <c r="F35" s="3">
+        <v>91</v>
+      </c>
+      <c r="G35" s="3">
+        <v>97</v>
+      </c>
+      <c r="H35" s="3">
+        <f t="shared" si="5"/>
+        <v>70</v>
+      </c>
+      <c r="T35" s="3">
+        <v>272</v>
+      </c>
+      <c r="U35" s="3">
+        <v>335</v>
+      </c>
+      <c r="V35" s="3">
+        <v>64</v>
+      </c>
+      <c r="W35" s="3">
+        <v>200</v>
+      </c>
+      <c r="X35" s="3">
+        <v>570</v>
+      </c>
+      <c r="Y35" s="3">
+        <v>683</v>
+      </c>
+      <c r="Z35" s="3">
+        <v>146</v>
+      </c>
+      <c r="AA35" s="3">
+        <v>216</v>
+      </c>
+      <c r="AB35" s="3">
+        <v>576</v>
+      </c>
+      <c r="AC35" s="3">
+        <v>777</v>
+      </c>
+      <c r="AD35" s="3">
+        <v>189</v>
+      </c>
+      <c r="AE35" s="3">
+        <v>256</v>
+      </c>
+      <c r="AF35" s="3">
+        <v>396</v>
+      </c>
+      <c r="AG35" s="3">
+        <v>618</v>
+      </c>
+      <c r="AH35" s="3">
+        <v>99</v>
+      </c>
+      <c r="AI35" s="3">
+        <v>246</v>
+      </c>
+      <c r="AJ35" s="3">
+        <v>206</v>
+      </c>
+      <c r="AK35" s="3">
+        <v>359</v>
+      </c>
+      <c r="AL35" s="3">
+        <v>66</v>
+      </c>
+      <c r="AM35" s="3">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="36" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C36" s="3">
+        <v>224</v>
+      </c>
+      <c r="D36" s="3">
+        <v>343</v>
+      </c>
+      <c r="E36" s="3">
+        <f t="shared" si="6"/>
+        <v>-119</v>
+      </c>
+      <c r="F36" s="3">
+        <v>90</v>
+      </c>
+      <c r="G36" s="3">
+        <v>97</v>
+      </c>
+      <c r="H36" s="3">
+        <f t="shared" si="5"/>
+        <v>68</v>
+      </c>
+      <c r="T36" s="3">
+        <v>270</v>
+      </c>
+      <c r="U36" s="3">
+        <v>338</v>
+      </c>
+      <c r="V36" s="3">
+        <v>63</v>
+      </c>
+      <c r="W36" s="3">
+        <v>199</v>
+      </c>
+      <c r="X36" s="3">
+        <v>565</v>
+      </c>
+      <c r="Y36" s="3">
+        <v>690</v>
+      </c>
+      <c r="Z36" s="3">
+        <v>144</v>
+      </c>
+      <c r="AA36" s="3">
+        <v>216</v>
+      </c>
+      <c r="AB36" s="3">
+        <v>572</v>
+      </c>
+      <c r="AC36" s="3">
+        <v>782</v>
+      </c>
+      <c r="AD36" s="3">
+        <v>186</v>
+      </c>
+      <c r="AE36" s="3">
+        <v>256</v>
+      </c>
+      <c r="AF36" s="3">
+        <v>391</v>
+      </c>
+      <c r="AG36" s="3">
+        <v>621</v>
+      </c>
+      <c r="AH36" s="3">
+        <v>99</v>
+      </c>
+      <c r="AI36" s="3">
+        <v>246</v>
+      </c>
+      <c r="AJ36" s="3">
+        <v>205</v>
+      </c>
+      <c r="AK36" s="3">
+        <v>363</v>
+      </c>
+      <c r="AL36" s="3">
+        <v>66</v>
+      </c>
+      <c r="AM36" s="3">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="37" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C37" s="3">
+        <v>222</v>
+      </c>
+      <c r="D37" s="3">
+        <v>346</v>
+      </c>
+      <c r="E37" s="3">
+        <f t="shared" si="6"/>
+        <v>-124</v>
+      </c>
+      <c r="F37" s="3">
+        <v>89</v>
+      </c>
+      <c r="G37" s="3">
+        <v>98</v>
+      </c>
+      <c r="H37" s="3">
+        <f t="shared" si="5"/>
+        <v>63</v>
+      </c>
+      <c r="T37" s="3">
+        <v>268</v>
+      </c>
+      <c r="U37" s="3">
+        <v>342</v>
+      </c>
+      <c r="V37" s="3">
+        <v>63</v>
+      </c>
+      <c r="W37" s="3">
+        <v>195</v>
+      </c>
+      <c r="X37" s="3">
+        <v>561</v>
+      </c>
+      <c r="Y37" s="3">
+        <v>697</v>
+      </c>
+      <c r="Z37" s="3">
+        <v>142</v>
+      </c>
+      <c r="AA37" s="3">
+        <v>216</v>
+      </c>
+      <c r="AB37" s="3">
+        <v>568</v>
+      </c>
+      <c r="AC37" s="3">
+        <v>788</v>
+      </c>
+      <c r="AD37" s="3">
+        <v>183</v>
+      </c>
+      <c r="AE37" s="3">
+        <v>254</v>
+      </c>
+      <c r="AF37" s="3">
+        <v>389</v>
+      </c>
+      <c r="AG37" s="3">
+        <v>624</v>
+      </c>
+      <c r="AH37" s="3">
+        <v>97</v>
+      </c>
+      <c r="AI37" s="3">
+        <v>245</v>
+      </c>
+      <c r="AJ37" s="3">
+        <v>204</v>
+      </c>
+      <c r="AK37" s="3">
+        <v>365</v>
+      </c>
+      <c r="AL37" s="3">
+        <v>64</v>
+      </c>
+      <c r="AM37" s="3">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="38" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C38" s="3">
+        <v>221</v>
+      </c>
+      <c r="D38" s="3">
+        <v>348</v>
+      </c>
+      <c r="E38" s="3">
+        <f t="shared" si="6"/>
+        <v>-127</v>
+      </c>
+      <c r="F38" s="3">
+        <v>88</v>
+      </c>
+      <c r="G38" s="3">
+        <v>99</v>
+      </c>
+      <c r="H38" s="3">
+        <f t="shared" si="5"/>
+        <v>60</v>
+      </c>
+      <c r="T38" s="3">
+        <v>266</v>
+      </c>
+      <c r="U38" s="3">
+        <v>343</v>
+      </c>
+      <c r="V38" s="3">
+        <v>61</v>
+      </c>
+      <c r="W38" s="3">
+        <v>192</v>
+      </c>
+      <c r="X38" s="3">
+        <v>558</v>
+      </c>
+      <c r="Y38" s="3">
+        <v>705</v>
+      </c>
+      <c r="Z38" s="3">
+        <v>140</v>
+      </c>
+      <c r="AA38" s="3">
+        <v>216</v>
+      </c>
+      <c r="AB38" s="3">
+        <v>562</v>
+      </c>
+      <c r="AC38" s="3">
+        <v>794</v>
+      </c>
+      <c r="AD38" s="3">
+        <v>182</v>
+      </c>
+      <c r="AE38" s="3">
+        <v>253</v>
+      </c>
+      <c r="AF38" s="3">
+        <v>386</v>
+      </c>
+      <c r="AG38" s="3">
+        <v>626</v>
+      </c>
+      <c r="AH38" s="3">
+        <v>97</v>
+      </c>
+      <c r="AI38" s="3">
+        <v>243</v>
+      </c>
+      <c r="AJ38" s="3">
+        <v>202</v>
+      </c>
+      <c r="AK38" s="3">
+        <v>368</v>
+      </c>
+      <c r="AL38" s="3">
+        <v>65</v>
+      </c>
+      <c r="AM38" s="3">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="39" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C39" s="3">
+        <v>219</v>
+      </c>
+      <c r="D39" s="3">
+        <v>351</v>
+      </c>
+      <c r="E39" s="3">
+        <f t="shared" si="6"/>
+        <v>-132</v>
+      </c>
+      <c r="F39" s="3">
+        <v>87</v>
+      </c>
+      <c r="G39" s="3">
+        <v>100</v>
+      </c>
+      <c r="H39" s="3">
+        <f t="shared" si="5"/>
+        <v>55</v>
+      </c>
+      <c r="T39" s="3">
+        <v>266</v>
+      </c>
+      <c r="U39" s="3">
+        <v>348</v>
+      </c>
+      <c r="V39" s="3">
+        <v>61</v>
+      </c>
+      <c r="W39" s="3">
+        <v>189</v>
+      </c>
+      <c r="X39" s="3">
+        <v>553</v>
+      </c>
+      <c r="Y39" s="3">
+        <v>712</v>
+      </c>
+      <c r="Z39" s="3">
+        <v>139</v>
+      </c>
+      <c r="AA39" s="3">
+        <v>215</v>
+      </c>
+      <c r="AB39" s="3">
+        <v>559</v>
+      </c>
+      <c r="AC39" s="3">
+        <v>801</v>
+      </c>
+      <c r="AD39" s="3">
+        <v>179</v>
+      </c>
+      <c r="AE39" s="3">
+        <v>250</v>
+      </c>
+      <c r="AF39" s="3">
+        <v>383</v>
+      </c>
+      <c r="AG39" s="3">
+        <v>628</v>
+      </c>
+      <c r="AH39" s="3">
+        <v>95</v>
+      </c>
+      <c r="AI39" s="3">
+        <v>241</v>
+      </c>
+      <c r="AJ39" s="3">
+        <v>201</v>
+      </c>
+      <c r="AK39" s="3">
+        <v>370</v>
+      </c>
+      <c r="AL39" s="3">
+        <v>63</v>
+      </c>
+      <c r="AM39" s="3">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="40" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B40" s="2"/>
+      <c r="C40" s="3">
+        <f>SUM(C15:C39)</f>
+        <v>5655</v>
+      </c>
+      <c r="D40" s="3">
+        <f>SUM(D15:D39)</f>
+        <v>7974</v>
+      </c>
+      <c r="E40" s="3">
+        <f>SUM(E15:E39)</f>
+        <v>-2319</v>
+      </c>
+      <c r="F40" s="3">
+        <f>SUM(F15:F39)</f>
+        <v>2436</v>
+      </c>
+      <c r="G40" s="3">
+        <f>SUM(G15:G39)</f>
+        <v>1762</v>
+      </c>
+      <c r="H40" s="3">
+        <f>E40+F40+G40</f>
+        <v>1879</v>
+      </c>
+      <c r="I40" s="3"/>
+      <c r="J40" s="3"/>
+      <c r="K40" s="3"/>
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+      <c r="N40" s="3"/>
+      <c r="O40" s="3"/>
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+      <c r="S40" s="3"/>
+      <c r="T40" s="3"/>
+      <c r="U40" s="3"/>
+      <c r="V40" s="3"/>
+      <c r="W40" s="3"/>
+      <c r="X40" s="3"/>
+      <c r="Y40" s="3"/>
+      <c r="Z40" s="3"/>
+      <c r="AA40" s="3"/>
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="3">
+        <v>255</v>
+      </c>
+      <c r="D41" s="3">
+        <v>238</v>
+      </c>
+      <c r="E41" s="3">
+        <f t="shared" si="6"/>
+        <v>17</v>
+      </c>
+      <c r="F41" s="3">
+        <v>70</v>
+      </c>
+      <c r="G41" s="3">
+        <v>71</v>
+      </c>
+      <c r="H41" s="3">
+        <f t="shared" ref="H41:H104" si="7">E41+F41+G41</f>
+        <v>158</v>
+      </c>
+      <c r="I41" s="3"/>
+      <c r="J41" s="3"/>
+      <c r="K41" s="3"/>
+      <c r="L41" s="3"/>
+      <c r="M41" s="3"/>
+      <c r="N41" s="3"/>
+      <c r="O41" s="3"/>
+      <c r="P41" s="3"/>
+      <c r="Q41" s="3"/>
+      <c r="R41" s="3"/>
+      <c r="S41" s="3"/>
+      <c r="T41" s="3"/>
+      <c r="U41" s="3"/>
+      <c r="V41" s="3"/>
+      <c r="W41" s="3"/>
+      <c r="X41" s="3"/>
+      <c r="Y41" s="3"/>
+      <c r="Z41" s="3"/>
+      <c r="AA41" s="3"/>
+      <c r="AB41" s="3"/>
+    </row>
+    <row r="42" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C42" s="3">
+        <v>253</v>
+      </c>
+      <c r="D42" s="3">
+        <v>241</v>
+      </c>
+      <c r="E42" s="3">
+        <f t="shared" si="6"/>
+        <v>12</v>
+      </c>
+      <c r="F42" s="3">
+        <v>72</v>
+      </c>
+      <c r="G42" s="3">
+        <v>104</v>
+      </c>
+      <c r="H42" s="3">
+        <f t="shared" si="7"/>
+        <v>188</v>
+      </c>
+    </row>
+    <row r="43" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="3">
+        <v>253</v>
+      </c>
+      <c r="D43" s="3">
+        <v>246</v>
+      </c>
+      <c r="E43" s="3">
+        <f t="shared" si="6"/>
+        <v>7</v>
+      </c>
+      <c r="F43" s="3">
+        <v>76</v>
+      </c>
+      <c r="G43" s="3">
+        <v>136</v>
+      </c>
+      <c r="H43" s="3">
+        <f t="shared" si="7"/>
+        <v>219</v>
+      </c>
+    </row>
+    <row r="44" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C44" s="3">
+        <v>255</v>
+      </c>
+      <c r="D44" s="3">
+        <v>251</v>
+      </c>
+      <c r="E44" s="3">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="F44" s="3">
+        <v>76</v>
+      </c>
+      <c r="G44" s="3">
+        <v>168</v>
+      </c>
+      <c r="H44" s="3">
+        <f t="shared" si="7"/>
+        <v>248</v>
+      </c>
+    </row>
+    <row r="45" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C45" s="3">
+        <v>257</v>
+      </c>
+      <c r="D45" s="3">
+        <v>256</v>
+      </c>
+      <c r="E45" s="3">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="F45" s="3">
+        <v>79</v>
+      </c>
+      <c r="G45" s="3">
+        <v>197</v>
+      </c>
+      <c r="H45" s="3">
+        <f t="shared" si="7"/>
+        <v>277</v>
+      </c>
+    </row>
+    <row r="46" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C46" s="3">
+        <v>259</v>
+      </c>
+      <c r="D46" s="3">
+        <v>262</v>
+      </c>
+      <c r="E46" s="3">
+        <f t="shared" si="6"/>
+        <v>-3</v>
+      </c>
+      <c r="F46" s="3">
+        <v>79</v>
+      </c>
+      <c r="G46" s="3">
+        <v>228</v>
+      </c>
+      <c r="H46" s="3">
+        <f t="shared" si="7"/>
+        <v>304</v>
+      </c>
+    </row>
+    <row r="47" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C47" s="3">
+        <v>264</v>
+      </c>
+      <c r="D47" s="3">
+        <v>268</v>
+      </c>
+      <c r="E47" s="3">
+        <f t="shared" si="6"/>
+        <v>-4</v>
+      </c>
+      <c r="F47" s="3">
+        <v>78</v>
+      </c>
+      <c r="G47" s="3">
+        <v>224</v>
+      </c>
+      <c r="H47" s="3">
+        <f t="shared" si="7"/>
+        <v>298</v>
+      </c>
+    </row>
+    <row r="48" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C48" s="3">
+        <v>267</v>
+      </c>
+      <c r="D48" s="3">
+        <v>274</v>
+      </c>
+      <c r="E48" s="3">
+        <f t="shared" si="6"/>
+        <v>-7</v>
+      </c>
+      <c r="F48" s="3">
+        <v>77</v>
+      </c>
+      <c r="G48" s="3">
+        <v>222</v>
+      </c>
+      <c r="H48" s="3">
+        <f t="shared" si="7"/>
+        <v>292</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49" s="3">
+        <v>271</v>
+      </c>
+      <c r="D49" s="3">
+        <v>280</v>
+      </c>
+      <c r="E49" s="3">
+        <f t="shared" si="6"/>
+        <v>-9</v>
+      </c>
+      <c r="F49" s="3">
+        <v>77</v>
+      </c>
+      <c r="G49" s="3">
+        <v>219</v>
+      </c>
+      <c r="H49" s="3">
+        <f t="shared" si="7"/>
+        <v>287</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C50" s="3">
+        <v>276</v>
+      </c>
+      <c r="D50" s="3">
+        <v>286</v>
+      </c>
+      <c r="E50" s="3">
+        <f t="shared" si="6"/>
+        <v>-10</v>
+      </c>
+      <c r="F50" s="3">
+        <v>76</v>
+      </c>
+      <c r="G50" s="3">
+        <v>217</v>
+      </c>
+      <c r="H50" s="3">
+        <f t="shared" si="7"/>
+        <v>283</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C51" s="3">
+        <v>277</v>
+      </c>
+      <c r="D51" s="3">
+        <v>292</v>
+      </c>
+      <c r="E51" s="3">
+        <f t="shared" si="6"/>
+        <v>-15</v>
+      </c>
+      <c r="F51" s="3">
+        <v>75</v>
+      </c>
+      <c r="G51" s="3">
+        <v>216</v>
+      </c>
+      <c r="H51" s="3">
+        <f t="shared" si="7"/>
+        <v>276</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C52" s="3">
+        <v>277</v>
+      </c>
+      <c r="D52" s="3">
+        <v>298</v>
+      </c>
+      <c r="E52" s="3">
+        <f t="shared" si="6"/>
+        <v>-21</v>
+      </c>
+      <c r="F52" s="3">
+        <v>74</v>
+      </c>
+      <c r="G52" s="3">
+        <v>215</v>
+      </c>
+      <c r="H52" s="3">
+        <f t="shared" si="7"/>
+        <v>268</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C53" s="3">
+        <v>278</v>
+      </c>
+      <c r="D53" s="3">
+        <v>303</v>
+      </c>
+      <c r="E53" s="3">
+        <f t="shared" si="6"/>
+        <v>-25</v>
+      </c>
+      <c r="F53" s="3">
+        <v>73</v>
+      </c>
+      <c r="G53" s="3">
+        <v>214</v>
+      </c>
+      <c r="H53" s="3">
+        <f t="shared" si="7"/>
+        <v>262</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C54" s="3">
+        <v>278</v>
+      </c>
+      <c r="D54" s="3">
+        <v>308</v>
+      </c>
+      <c r="E54" s="3">
+        <f t="shared" si="6"/>
+        <v>-30</v>
+      </c>
+      <c r="F54" s="3">
+        <v>72</v>
+      </c>
+      <c r="G54" s="3">
+        <v>213</v>
+      </c>
+      <c r="H54" s="3">
+        <f>E54+F54+G54</f>
+        <v>255</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C55" s="3">
+        <v>279</v>
+      </c>
+      <c r="D55" s="3">
+        <v>313</v>
+      </c>
+      <c r="E55" s="3">
+        <f t="shared" si="6"/>
+        <v>-34</v>
+      </c>
+      <c r="F55" s="3">
+        <v>70</v>
+      </c>
+      <c r="G55" s="3">
+        <v>212</v>
+      </c>
+      <c r="H55" s="3">
+        <f t="shared" si="7"/>
+        <v>248</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C56" s="3">
+        <v>278</v>
+      </c>
+      <c r="D56" s="3">
+        <v>317</v>
+      </c>
+      <c r="E56" s="3">
+        <f t="shared" si="6"/>
+        <v>-39</v>
+      </c>
+      <c r="F56" s="3">
+        <v>70</v>
+      </c>
+      <c r="G56" s="3">
+        <v>210</v>
+      </c>
+      <c r="H56" s="3">
+        <f t="shared" si="7"/>
+        <v>241</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="3">
+        <v>278</v>
+      </c>
+      <c r="D57" s="3">
+        <v>322</v>
+      </c>
+      <c r="E57" s="3">
+        <f t="shared" si="6"/>
+        <v>-44</v>
+      </c>
+      <c r="F57" s="3">
+        <v>69</v>
+      </c>
+      <c r="G57" s="3">
+        <v>209</v>
+      </c>
+      <c r="H57" s="3">
+        <f t="shared" si="7"/>
+        <v>234</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C58" s="3">
+        <v>276</v>
+      </c>
+      <c r="D58" s="3">
+        <v>325</v>
+      </c>
+      <c r="E58" s="3">
+        <f t="shared" si="6"/>
+        <v>-49</v>
+      </c>
+      <c r="F58" s="3">
+        <v>67</v>
+      </c>
+      <c r="G58" s="3">
+        <v>207</v>
+      </c>
+      <c r="H58" s="3">
+        <f t="shared" si="7"/>
+        <v>225</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C59" s="3">
+        <v>275</v>
+      </c>
+      <c r="D59" s="3">
+        <v>328</v>
+      </c>
+      <c r="E59" s="3">
+        <f t="shared" si="6"/>
+        <v>-53</v>
+      </c>
+      <c r="F59" s="3">
+        <v>66</v>
+      </c>
+      <c r="G59" s="3">
+        <v>206</v>
+      </c>
+      <c r="H59" s="3">
+        <f t="shared" si="7"/>
+        <v>219</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C60" s="3">
+        <v>273</v>
+      </c>
+      <c r="D60" s="3">
+        <v>332</v>
+      </c>
+      <c r="E60" s="3">
+        <f t="shared" si="6"/>
+        <v>-59</v>
+      </c>
+      <c r="F60" s="3">
+        <v>66</v>
+      </c>
+      <c r="G60" s="3">
+        <v>203</v>
+      </c>
+      <c r="H60" s="3">
+        <f t="shared" si="7"/>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C61" s="3">
+        <v>272</v>
+      </c>
+      <c r="D61" s="3">
+        <v>335</v>
+      </c>
+      <c r="E61" s="3">
+        <f t="shared" si="6"/>
+        <v>-63</v>
+      </c>
+      <c r="F61" s="3">
+        <v>64</v>
+      </c>
+      <c r="G61" s="3">
+        <v>200</v>
+      </c>
+      <c r="H61" s="3">
+        <f t="shared" si="7"/>
+        <v>201</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C62" s="3">
+        <v>270</v>
+      </c>
+      <c r="D62" s="3">
+        <v>338</v>
+      </c>
+      <c r="E62" s="3">
+        <f t="shared" si="6"/>
+        <v>-68</v>
+      </c>
+      <c r="F62" s="3">
+        <v>63</v>
+      </c>
+      <c r="G62" s="3">
+        <v>199</v>
+      </c>
+      <c r="H62" s="3">
+        <f t="shared" si="7"/>
+        <v>194</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C63" s="3">
+        <v>268</v>
+      </c>
+      <c r="D63" s="3">
+        <v>342</v>
+      </c>
+      <c r="E63" s="3">
+        <f t="shared" si="6"/>
+        <v>-74</v>
+      </c>
+      <c r="F63" s="3">
+        <v>63</v>
+      </c>
+      <c r="G63" s="3">
+        <v>195</v>
+      </c>
+      <c r="H63" s="3">
+        <f t="shared" si="7"/>
+        <v>184</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="3">
+        <v>266</v>
+      </c>
+      <c r="D64" s="3">
+        <v>343</v>
+      </c>
+      <c r="E64" s="3">
+        <f t="shared" si="6"/>
+        <v>-77</v>
+      </c>
+      <c r="F64" s="3">
+        <v>61</v>
+      </c>
+      <c r="G64" s="3">
+        <v>192</v>
+      </c>
+      <c r="H64" s="3">
+        <f t="shared" si="7"/>
+        <v>176</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C65" s="3">
+        <v>266</v>
+      </c>
+      <c r="D65" s="3">
+        <v>348</v>
+      </c>
+      <c r="E65" s="3">
+        <f t="shared" si="6"/>
+        <v>-82</v>
+      </c>
+      <c r="F65" s="3">
+        <v>61</v>
+      </c>
+      <c r="G65" s="3">
+        <v>189</v>
+      </c>
+      <c r="H65" s="3">
+        <f t="shared" si="7"/>
+        <v>168</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B66" s="2"/>
+      <c r="C66" s="3">
+        <f>SUM(C41:C65)</f>
+        <v>6721</v>
+      </c>
+      <c r="D66" s="3">
+        <f>SUM(D41:D65)</f>
+        <v>7446</v>
+      </c>
+      <c r="E66" s="3">
+        <f>SUM(E41:E65)</f>
+        <v>-725</v>
+      </c>
+      <c r="F66" s="3">
+        <f>SUM(F41:F65)</f>
+        <v>1774</v>
+      </c>
+      <c r="G66" s="3">
+        <f>SUM(G41:G65)</f>
+        <v>4866</v>
+      </c>
+      <c r="H66" s="3">
+        <f t="shared" si="7"/>
+        <v>5915</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C67" s="3">
+        <v>555</v>
+      </c>
+      <c r="D67" s="3">
+        <v>519</v>
+      </c>
+      <c r="E67" s="3">
+        <f t="shared" si="6"/>
+        <v>36</v>
+      </c>
+      <c r="F67" s="3">
+        <v>214</v>
+      </c>
+      <c r="G67" s="3">
+        <v>143</v>
+      </c>
+      <c r="H67" s="3">
+        <f t="shared" si="7"/>
+        <v>393</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C68" s="3">
+        <v>554</v>
+      </c>
+      <c r="D68" s="3">
+        <v>524</v>
+      </c>
+      <c r="E68" s="3">
+        <f t="shared" si="6"/>
+        <v>30</v>
+      </c>
+      <c r="F68" s="3">
+        <v>206</v>
+      </c>
+      <c r="G68" s="3">
+        <v>164</v>
+      </c>
+      <c r="H68" s="3">
+        <f t="shared" si="7"/>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C69" s="3">
+        <v>556</v>
+      </c>
+      <c r="D69" s="3">
+        <v>528</v>
+      </c>
+      <c r="E69" s="3">
+        <f t="shared" si="6"/>
+        <v>28</v>
+      </c>
+      <c r="F69" s="3">
+        <v>197</v>
+      </c>
+      <c r="G69" s="3">
+        <v>181</v>
+      </c>
+      <c r="H69" s="3">
+        <f t="shared" si="7"/>
+        <v>406</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C70" s="3">
+        <v>556</v>
+      </c>
+      <c r="D70" s="3">
+        <v>536</v>
+      </c>
+      <c r="E70" s="3">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+      <c r="F70" s="3">
+        <v>190</v>
+      </c>
+      <c r="G70" s="3">
+        <v>197</v>
+      </c>
+      <c r="H70" s="3">
+        <f t="shared" si="7"/>
+        <v>407</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C71" s="3">
+        <v>559</v>
+      </c>
+      <c r="D71" s="3">
+        <v>543</v>
+      </c>
+      <c r="E71" s="3">
+        <f t="shared" si="6"/>
+        <v>16</v>
+      </c>
+      <c r="F71" s="3">
+        <v>180</v>
+      </c>
+      <c r="G71" s="3">
+        <v>212</v>
+      </c>
+      <c r="H71" s="3">
+        <f t="shared" si="7"/>
+        <v>408</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C72" s="3">
+        <v>562</v>
+      </c>
+      <c r="D72" s="3">
+        <v>551</v>
+      </c>
+      <c r="E72" s="3">
+        <f t="shared" si="6"/>
+        <v>11</v>
+      </c>
+      <c r="F72" s="3">
+        <v>169</v>
+      </c>
+      <c r="G72" s="3">
+        <v>227</v>
+      </c>
+      <c r="H72" s="3">
+        <f t="shared" si="7"/>
+        <v>407</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C73" s="3">
+        <v>566</v>
+      </c>
+      <c r="D73" s="3">
+        <v>559</v>
+      </c>
+      <c r="E73" s="3">
+        <f t="shared" si="6"/>
+        <v>7</v>
+      </c>
+      <c r="F73" s="3">
+        <v>167</v>
+      </c>
+      <c r="G73" s="3">
+        <v>224</v>
+      </c>
+      <c r="H73" s="3">
+        <f t="shared" si="7"/>
+        <v>398</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C74" s="3">
+        <v>572</v>
+      </c>
+      <c r="D74" s="3">
+        <v>570</v>
+      </c>
+      <c r="E74" s="3">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="F74" s="3">
+        <v>168</v>
+      </c>
+      <c r="G74" s="3">
+        <v>221</v>
+      </c>
+      <c r="H74" s="3">
+        <f t="shared" si="7"/>
+        <v>391</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C75" s="3">
+        <v>576</v>
+      </c>
+      <c r="D75" s="3">
+        <v>579</v>
+      </c>
+      <c r="E75" s="3">
+        <f t="shared" si="6"/>
+        <v>-3</v>
+      </c>
+      <c r="F75" s="3">
+        <v>168</v>
+      </c>
+      <c r="G75" s="3">
+        <v>221</v>
+      </c>
+      <c r="H75" s="3">
+        <f t="shared" si="7"/>
+        <v>386</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C76" s="3">
+        <v>583</v>
+      </c>
+      <c r="D76" s="3">
+        <v>589</v>
+      </c>
+      <c r="E76" s="3">
+        <f t="shared" si="6"/>
+        <v>-6</v>
+      </c>
+      <c r="F76" s="3">
+        <v>166</v>
+      </c>
+      <c r="G76" s="3">
+        <v>221</v>
+      </c>
+      <c r="H76" s="3">
+        <f t="shared" si="7"/>
+        <v>381</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C77" s="3">
+        <v>584</v>
+      </c>
+      <c r="D77" s="3">
+        <v>599</v>
+      </c>
+      <c r="E77" s="3">
+        <f t="shared" si="6"/>
+        <v>-15</v>
+      </c>
+      <c r="F77" s="3">
+        <v>165</v>
+      </c>
+      <c r="G77" s="3">
+        <v>220</v>
+      </c>
+      <c r="H77" s="3">
+        <f t="shared" si="7"/>
+        <v>370</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C78" s="3">
+        <v>585</v>
+      </c>
+      <c r="D78" s="3">
+        <v>609</v>
+      </c>
+      <c r="E78" s="3">
+        <f t="shared" si="6"/>
+        <v>-24</v>
+      </c>
+      <c r="F78" s="3">
+        <v>163</v>
+      </c>
+      <c r="G78" s="3">
+        <v>220</v>
+      </c>
+      <c r="H78" s="3">
+        <f t="shared" si="7"/>
+        <v>359</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C79" s="3">
+        <v>586</v>
+      </c>
+      <c r="D79" s="3">
+        <v>619</v>
+      </c>
+      <c r="E79" s="3">
+        <f t="shared" si="6"/>
+        <v>-33</v>
+      </c>
+      <c r="F79" s="3">
+        <v>161</v>
+      </c>
+      <c r="G79" s="3">
+        <v>220</v>
+      </c>
+      <c r="H79" s="3">
+        <f t="shared" si="7"/>
+        <v>348</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C80" s="3">
+        <v>585</v>
+      </c>
+      <c r="D80" s="3">
+        <v>628</v>
+      </c>
+      <c r="E80" s="3">
+        <f t="shared" si="6"/>
+        <v>-43</v>
+      </c>
+      <c r="F80" s="3">
+        <v>160</v>
+      </c>
+      <c r="G80" s="3">
+        <v>219</v>
+      </c>
+      <c r="H80" s="3">
+        <f t="shared" si="7"/>
+        <v>336</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C81" s="3">
+        <v>586</v>
+      </c>
+      <c r="D81" s="3">
+        <v>637</v>
+      </c>
+      <c r="E81" s="3">
+        <f t="shared" si="6"/>
+        <v>-51</v>
+      </c>
+      <c r="F81" s="3">
+        <v>157</v>
+      </c>
+      <c r="G81" s="3">
+        <v>218</v>
+      </c>
+      <c r="H81" s="3">
+        <f t="shared" si="7"/>
+        <v>324</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C82" s="3">
+        <v>584</v>
+      </c>
+      <c r="D82" s="3">
+        <v>645</v>
+      </c>
+      <c r="E82" s="3">
+        <f t="shared" ref="E82:E148" si="8">C82-D82</f>
+        <v>-61</v>
+      </c>
+      <c r="F82" s="3">
+        <v>155</v>
+      </c>
+      <c r="G82" s="3">
+        <v>220</v>
+      </c>
+      <c r="H82" s="3">
+        <f t="shared" si="7"/>
+        <v>314</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C83" s="3">
+        <v>583</v>
+      </c>
+      <c r="D83" s="3">
+        <v>654</v>
+      </c>
+      <c r="E83" s="3">
+        <f t="shared" si="8"/>
+        <v>-71</v>
+      </c>
+      <c r="F83" s="3">
+        <v>154</v>
+      </c>
+      <c r="G83" s="3">
+        <v>219</v>
+      </c>
+      <c r="H83" s="3">
+        <f t="shared" si="7"/>
+        <v>302</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C84" s="3">
+        <v>580</v>
+      </c>
+      <c r="D84" s="3">
+        <v>661</v>
+      </c>
+      <c r="E84" s="3">
+        <f t="shared" si="8"/>
+        <v>-81</v>
+      </c>
+      <c r="F84" s="3">
+        <v>152</v>
+      </c>
+      <c r="G84" s="3">
+        <v>219</v>
+      </c>
+      <c r="H84" s="3">
+        <f t="shared" si="7"/>
+        <v>290</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C85" s="3">
+        <v>577</v>
+      </c>
+      <c r="D85" s="3">
+        <v>668</v>
+      </c>
+      <c r="E85" s="3">
+        <f t="shared" si="8"/>
+        <v>-91</v>
+      </c>
+      <c r="F85" s="3">
+        <v>149</v>
+      </c>
+      <c r="G85" s="3">
+        <v>217</v>
+      </c>
+      <c r="H85" s="3">
+        <f t="shared" si="7"/>
+        <v>275</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C86" s="3">
+        <v>573</v>
+      </c>
+      <c r="D86" s="3">
+        <v>676</v>
+      </c>
+      <c r="E86" s="3">
+        <f t="shared" si="8"/>
+        <v>-103</v>
+      </c>
+      <c r="F86" s="3">
+        <v>148</v>
+      </c>
+      <c r="G86" s="3">
+        <v>217</v>
+      </c>
+      <c r="H86" s="3">
+        <f t="shared" si="7"/>
+        <v>262</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C87" s="3">
+        <v>570</v>
+      </c>
+      <c r="D87" s="3">
+        <v>683</v>
+      </c>
+      <c r="E87" s="3">
+        <f t="shared" si="8"/>
+        <v>-113</v>
+      </c>
+      <c r="F87" s="3">
+        <v>146</v>
+      </c>
+      <c r="G87" s="3">
+        <v>216</v>
+      </c>
+      <c r="H87" s="3">
+        <f t="shared" si="7"/>
+        <v>249</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C88" s="3">
+        <v>565</v>
+      </c>
+      <c r="D88" s="3">
+        <v>690</v>
+      </c>
+      <c r="E88" s="3">
+        <f t="shared" si="8"/>
+        <v>-125</v>
+      </c>
+      <c r="F88" s="3">
+        <v>144</v>
+      </c>
+      <c r="G88" s="3">
+        <v>216</v>
+      </c>
+      <c r="H88" s="3">
+        <f t="shared" si="7"/>
+        <v>235</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C89" s="3">
+        <v>561</v>
+      </c>
+      <c r="D89" s="3">
+        <v>697</v>
+      </c>
+      <c r="E89" s="3">
+        <f t="shared" si="8"/>
+        <v>-136</v>
+      </c>
+      <c r="F89" s="3">
+        <v>142</v>
+      </c>
+      <c r="G89" s="3">
+        <v>216</v>
+      </c>
+      <c r="H89" s="3">
+        <f t="shared" si="7"/>
+        <v>222</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C90" s="3">
+        <v>558</v>
+      </c>
+      <c r="D90" s="3">
+        <v>705</v>
+      </c>
+      <c r="E90" s="3">
+        <f t="shared" si="8"/>
+        <v>-147</v>
+      </c>
+      <c r="F90" s="3">
+        <v>140</v>
+      </c>
+      <c r="G90" s="3">
+        <v>216</v>
+      </c>
+      <c r="H90" s="3">
+        <f t="shared" si="7"/>
+        <v>209</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C91" s="3">
+        <v>553</v>
+      </c>
+      <c r="D91" s="3">
+        <v>712</v>
+      </c>
+      <c r="E91" s="3">
+        <f t="shared" si="8"/>
+        <v>-159</v>
+      </c>
+      <c r="F91" s="3">
+        <v>139</v>
+      </c>
+      <c r="G91" s="3">
+        <v>215</v>
+      </c>
+      <c r="H91" s="3">
+        <f t="shared" si="7"/>
+        <v>195</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" s="2"/>
+      <c r="B92" s="2"/>
+      <c r="C92" s="3">
+        <f>SUM(C67:C91)</f>
+        <v>14269</v>
+      </c>
+      <c r="D92" s="3">
+        <f>SUM(D67:D91)</f>
+        <v>15381</v>
+      </c>
+      <c r="E92" s="3">
+        <f>SUM(E67:E91)</f>
+        <v>-1112</v>
+      </c>
+      <c r="F92" s="3">
+        <f>SUM(F67:F91)</f>
+        <v>4100</v>
+      </c>
+      <c r="G92" s="3">
+        <f>SUM(G67:G91)</f>
+        <v>5279</v>
+      </c>
+      <c r="H92" s="3">
+        <f t="shared" si="7"/>
+        <v>8267</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C93" s="3">
+        <v>556</v>
+      </c>
+      <c r="D93" s="3">
+        <v>615</v>
+      </c>
+      <c r="E93" s="3">
+        <f t="shared" si="8"/>
+        <v>-59</v>
+      </c>
+      <c r="F93" s="3">
+        <v>171</v>
+      </c>
+      <c r="G93" s="3">
+        <v>174</v>
+      </c>
+      <c r="H93" s="3">
+        <f t="shared" si="7"/>
+        <v>286</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C94" s="3">
+        <v>556</v>
+      </c>
+      <c r="D94" s="3">
+        <v>619</v>
+      </c>
+      <c r="E94" s="3">
+        <f t="shared" si="8"/>
+        <v>-63</v>
+      </c>
+      <c r="F94" s="3">
+        <v>181</v>
+      </c>
+      <c r="G94" s="3">
+        <v>191</v>
+      </c>
+      <c r="H94" s="3">
+        <f t="shared" si="7"/>
+        <v>309</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C95" s="3">
+        <v>558</v>
+      </c>
+      <c r="D95" s="3">
+        <v>626</v>
+      </c>
+      <c r="E95" s="3">
+        <f t="shared" si="8"/>
+        <v>-68</v>
+      </c>
+      <c r="F95" s="3">
+        <v>192</v>
+      </c>
+      <c r="G95" s="3">
+        <v>206</v>
+      </c>
+      <c r="H95" s="3">
+        <f t="shared" si="7"/>
+        <v>330</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C96" s="3">
+        <v>560</v>
+      </c>
+      <c r="D96" s="3">
+        <v>634</v>
+      </c>
+      <c r="E96" s="3">
+        <f t="shared" si="8"/>
+        <v>-74</v>
+      </c>
+      <c r="F96" s="3">
+        <v>203</v>
+      </c>
+      <c r="G96" s="3">
+        <v>218</v>
+      </c>
+      <c r="H96" s="3">
+        <f t="shared" si="7"/>
+        <v>347</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C97" s="3">
+        <v>562</v>
+      </c>
+      <c r="D97" s="3">
+        <v>643</v>
+      </c>
+      <c r="E97" s="3">
+        <f t="shared" si="8"/>
+        <v>-81</v>
+      </c>
+      <c r="F97" s="3">
+        <v>210</v>
+      </c>
+      <c r="G97" s="3">
+        <v>228</v>
+      </c>
+      <c r="H97" s="3">
+        <f t="shared" si="7"/>
+        <v>357</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C98" s="3">
+        <v>567</v>
+      </c>
+      <c r="D98" s="3">
+        <v>651</v>
+      </c>
+      <c r="E98" s="3">
+        <f t="shared" si="8"/>
+        <v>-84</v>
+      </c>
+      <c r="F98" s="3">
+        <v>215</v>
+      </c>
+      <c r="G98" s="3">
+        <v>235</v>
+      </c>
+      <c r="H98" s="3">
+        <f t="shared" si="7"/>
+        <v>366</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C99" s="3">
+        <v>572</v>
+      </c>
+      <c r="D99" s="3">
+        <v>662</v>
+      </c>
+      <c r="E99" s="3">
+        <f t="shared" si="8"/>
+        <v>-90</v>
+      </c>
+      <c r="F99" s="3">
+        <v>213</v>
+      </c>
+      <c r="G99" s="3">
+        <v>233</v>
+      </c>
+      <c r="H99" s="3">
+        <f t="shared" si="7"/>
+        <v>356</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C100" s="3">
+        <v>578</v>
+      </c>
+      <c r="D100" s="3">
+        <v>673</v>
+      </c>
+      <c r="E100" s="3">
+        <f t="shared" si="8"/>
+        <v>-95</v>
+      </c>
+      <c r="F100" s="3">
+        <v>215</v>
+      </c>
+      <c r="G100" s="3">
+        <v>232</v>
+      </c>
+      <c r="H100" s="3">
+        <f t="shared" si="7"/>
+        <v>352</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C101" s="3">
+        <v>584</v>
+      </c>
+      <c r="D101" s="3">
+        <v>682</v>
+      </c>
+      <c r="E101" s="3">
+        <f t="shared" si="8"/>
+        <v>-98</v>
+      </c>
+      <c r="F101" s="3">
+        <v>215</v>
+      </c>
+      <c r="G101" s="3">
+        <v>230</v>
+      </c>
+      <c r="H101" s="3">
+        <f t="shared" si="7"/>
+        <v>347</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C102" s="3">
+        <v>592</v>
+      </c>
+      <c r="D102" s="3">
+        <v>693</v>
+      </c>
+      <c r="E102" s="3">
+        <f t="shared" si="8"/>
+        <v>-101</v>
+      </c>
+      <c r="F102" s="3">
+        <v>213</v>
+      </c>
+      <c r="G102" s="3">
+        <v>230</v>
+      </c>
+      <c r="H102" s="3">
+        <f t="shared" si="7"/>
+        <v>342</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C103" s="3">
+        <v>593</v>
+      </c>
+      <c r="D103" s="3">
+        <v>704</v>
+      </c>
+      <c r="E103" s="3">
+        <f t="shared" si="8"/>
+        <v>-111</v>
+      </c>
+      <c r="F103" s="3">
+        <v>212</v>
+      </c>
+      <c r="G103" s="3">
+        <v>230</v>
+      </c>
+      <c r="H103" s="3">
+        <f t="shared" si="7"/>
+        <v>331</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C104" s="3">
+        <v>594</v>
+      </c>
+      <c r="D104" s="3">
+        <v>713</v>
+      </c>
+      <c r="E104" s="3">
+        <f t="shared" si="8"/>
+        <v>-119</v>
+      </c>
+      <c r="F104" s="3">
+        <v>210</v>
+      </c>
+      <c r="G104" s="3">
+        <v>232</v>
+      </c>
+      <c r="H104" s="3">
+        <f t="shared" si="7"/>
+        <v>323</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C105" s="3">
+        <v>595</v>
+      </c>
+      <c r="D105" s="3">
+        <v>724</v>
+      </c>
+      <c r="E105" s="3">
+        <f t="shared" si="8"/>
+        <v>-129</v>
+      </c>
+      <c r="F105" s="3">
+        <v>208</v>
+      </c>
+      <c r="G105" s="3">
+        <v>235</v>
+      </c>
+      <c r="H105" s="3">
+        <f t="shared" ref="H105:H168" si="9">E105+F105+G105</f>
+        <v>314</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C106" s="3">
+        <v>596</v>
+      </c>
+      <c r="D106" s="3">
+        <v>731</v>
+      </c>
+      <c r="E106" s="3">
+        <f t="shared" si="8"/>
+        <v>-135</v>
+      </c>
+      <c r="F106" s="3">
+        <v>206</v>
+      </c>
+      <c r="G106" s="3">
+        <v>238</v>
+      </c>
+      <c r="H106" s="3">
+        <f t="shared" si="9"/>
+        <v>309</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C107" s="3">
+        <v>594</v>
+      </c>
+      <c r="D107" s="3">
+        <v>740</v>
+      </c>
+      <c r="E107" s="3">
+        <f t="shared" si="8"/>
+        <v>-146</v>
+      </c>
+      <c r="F107" s="3">
+        <v>204</v>
+      </c>
+      <c r="G107" s="3">
+        <v>244</v>
+      </c>
+      <c r="H107" s="3">
+        <f t="shared" si="9"/>
+        <v>302</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C108" s="3">
+        <v>593</v>
+      </c>
+      <c r="D108" s="3">
+        <v>746</v>
+      </c>
+      <c r="E108" s="3">
+        <f t="shared" si="8"/>
+        <v>-153</v>
+      </c>
+      <c r="F108" s="3">
+        <v>201</v>
+      </c>
+      <c r="G108" s="3">
+        <v>247</v>
+      </c>
+      <c r="H108" s="3">
+        <f t="shared" si="9"/>
+        <v>295</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C109" s="3">
+        <v>591</v>
+      </c>
+      <c r="D109" s="3">
+        <v>754</v>
+      </c>
+      <c r="E109" s="3">
+        <f t="shared" si="8"/>
+        <v>-163</v>
+      </c>
+      <c r="F109" s="3">
+        <v>200</v>
+      </c>
+      <c r="G109" s="3">
+        <v>252</v>
+      </c>
+      <c r="H109" s="3">
+        <f t="shared" si="9"/>
+        <v>289</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C110" s="3">
+        <v>588</v>
+      </c>
+      <c r="D110" s="3">
+        <v>759</v>
+      </c>
+      <c r="E110" s="3">
+        <f t="shared" si="8"/>
+        <v>-171</v>
+      </c>
+      <c r="F110" s="3">
+        <v>196</v>
+      </c>
+      <c r="G110" s="3">
+        <v>254</v>
+      </c>
+      <c r="H110" s="3">
+        <f t="shared" si="9"/>
+        <v>279</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C111" s="3">
+        <v>584</v>
+      </c>
+      <c r="D111" s="3">
+        <v>765</v>
+      </c>
+      <c r="E111" s="3">
+        <f t="shared" si="8"/>
+        <v>-181</v>
+      </c>
+      <c r="F111" s="3">
+        <v>195</v>
+      </c>
+      <c r="G111" s="3">
+        <v>255</v>
+      </c>
+      <c r="H111" s="3">
+        <f t="shared" si="9"/>
+        <v>269</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C112" s="3">
+        <v>581</v>
+      </c>
+      <c r="D112" s="3">
+        <v>771</v>
+      </c>
+      <c r="E112" s="3">
+        <f t="shared" si="8"/>
+        <v>-190</v>
+      </c>
+      <c r="F112" s="3">
+        <v>192</v>
+      </c>
+      <c r="G112" s="3">
+        <v>256</v>
+      </c>
+      <c r="H112" s="3">
+        <f t="shared" si="9"/>
+        <v>258</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C113" s="3">
+        <v>576</v>
+      </c>
+      <c r="D113" s="3">
+        <v>777</v>
+      </c>
+      <c r="E113" s="3">
+        <f t="shared" si="8"/>
+        <v>-201</v>
+      </c>
+      <c r="F113" s="3">
+        <v>189</v>
+      </c>
+      <c r="G113" s="3">
+        <v>256</v>
+      </c>
+      <c r="H113" s="3">
+        <f t="shared" si="9"/>
+        <v>244</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C114" s="3">
+        <v>572</v>
+      </c>
+      <c r="D114" s="3">
+        <v>782</v>
+      </c>
+      <c r="E114" s="3">
+        <f t="shared" si="8"/>
+        <v>-210</v>
+      </c>
+      <c r="F114" s="3">
+        <v>186</v>
+      </c>
+      <c r="G114" s="3">
+        <v>256</v>
+      </c>
+      <c r="H114" s="3">
+        <f t="shared" si="9"/>
+        <v>232</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C115" s="3">
+        <v>568</v>
+      </c>
+      <c r="D115" s="3">
+        <v>788</v>
+      </c>
+      <c r="E115" s="3">
+        <f t="shared" si="8"/>
+        <v>-220</v>
+      </c>
+      <c r="F115" s="3">
+        <v>183</v>
+      </c>
+      <c r="G115" s="3">
+        <v>254</v>
+      </c>
+      <c r="H115" s="3">
+        <f t="shared" si="9"/>
+        <v>217</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C116" s="3">
+        <v>562</v>
+      </c>
+      <c r="D116" s="3">
+        <v>794</v>
+      </c>
+      <c r="E116" s="3">
+        <f t="shared" si="8"/>
+        <v>-232</v>
+      </c>
+      <c r="F116" s="3">
+        <v>182</v>
+      </c>
+      <c r="G116" s="3">
+        <v>253</v>
+      </c>
+      <c r="H116" s="3">
+        <f t="shared" si="9"/>
+        <v>203</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C117" s="3">
+        <v>559</v>
+      </c>
+      <c r="D117" s="3">
+        <v>801</v>
+      </c>
+      <c r="E117" s="3">
+        <f t="shared" si="8"/>
+        <v>-242</v>
+      </c>
+      <c r="F117" s="3">
+        <v>179</v>
+      </c>
+      <c r="G117" s="3">
+        <v>250</v>
+      </c>
+      <c r="H117" s="3">
+        <f t="shared" si="9"/>
+        <v>187</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" s="2"/>
+      <c r="B118" s="2"/>
+      <c r="C118" s="3">
+        <f>SUM(C93:C117)</f>
+        <v>14431</v>
+      </c>
+      <c r="D118" s="3">
+        <f>SUM(D93:D117)</f>
+        <v>17847</v>
+      </c>
+      <c r="E118" s="3">
+        <f>SUM(E93:E117)</f>
+        <v>-3416</v>
+      </c>
+      <c r="F118" s="3">
+        <f>SUM(F93:F117)</f>
+        <v>4971</v>
+      </c>
+      <c r="G118" s="3">
+        <f>SUM(G93:G117)</f>
+        <v>5889</v>
+      </c>
+      <c r="H118" s="3">
+        <f t="shared" si="9"/>
+        <v>7444</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C119" s="3">
+        <v>385</v>
+      </c>
+      <c r="D119" s="3">
+        <v>480</v>
+      </c>
+      <c r="E119" s="3">
+        <f t="shared" si="8"/>
+        <v>-95</v>
+      </c>
+      <c r="F119" s="3">
+        <v>60</v>
+      </c>
+      <c r="G119" s="3">
+        <v>110</v>
+      </c>
+      <c r="H119" s="3">
+        <f t="shared" si="9"/>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C120" s="3">
+        <v>387</v>
+      </c>
+      <c r="D120" s="3">
+        <v>485</v>
+      </c>
+      <c r="E120" s="3">
+        <f t="shared" si="8"/>
+        <v>-98</v>
+      </c>
+      <c r="F120" s="3">
+        <v>72</v>
+      </c>
+      <c r="G120" s="3">
+        <v>126</v>
+      </c>
+      <c r="H120" s="3">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C121" s="3">
+        <v>389</v>
+      </c>
+      <c r="D121" s="3">
+        <v>489</v>
+      </c>
+      <c r="E121" s="3">
+        <f t="shared" si="8"/>
+        <v>-100</v>
+      </c>
+      <c r="F121" s="3">
+        <v>83</v>
+      </c>
+      <c r="G121" s="3">
+        <v>141</v>
+      </c>
+      <c r="H121" s="3">
+        <f t="shared" si="9"/>
+        <v>124</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C122" s="3">
+        <v>393</v>
+      </c>
+      <c r="D122" s="3">
+        <v>496</v>
+      </c>
+      <c r="E122" s="3">
+        <f t="shared" si="8"/>
+        <v>-103</v>
+      </c>
+      <c r="F122" s="3">
+        <v>94</v>
+      </c>
+      <c r="G122" s="3">
+        <v>156</v>
+      </c>
+      <c r="H122" s="3">
+        <f t="shared" si="9"/>
+        <v>147</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C123" s="3">
+        <v>395</v>
+      </c>
+      <c r="D123" s="3">
+        <v>504</v>
+      </c>
+      <c r="E123" s="3">
+        <f t="shared" si="8"/>
+        <v>-109</v>
+      </c>
+      <c r="F123" s="3">
+        <v>104</v>
+      </c>
+      <c r="G123" s="3">
+        <v>172</v>
+      </c>
+      <c r="H123" s="3">
+        <f t="shared" si="9"/>
+        <v>167</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C124" s="3">
+        <v>399</v>
+      </c>
+      <c r="D124" s="3">
+        <v>511</v>
+      </c>
+      <c r="E124" s="3">
+        <f t="shared" si="8"/>
+        <v>-112</v>
+      </c>
+      <c r="F124" s="3">
+        <v>112</v>
+      </c>
+      <c r="G124" s="3">
+        <v>186</v>
+      </c>
+      <c r="H124" s="3">
+        <f t="shared" si="9"/>
+        <v>186</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C125" s="3">
+        <v>403</v>
+      </c>
+      <c r="D125" s="3">
+        <v>519</v>
+      </c>
+      <c r="E125" s="3">
+        <f t="shared" si="8"/>
+        <v>-116</v>
+      </c>
+      <c r="F125" s="3">
+        <v>111</v>
+      </c>
+      <c r="G125" s="3">
+        <v>193</v>
+      </c>
+      <c r="H125" s="3">
+        <f t="shared" si="9"/>
+        <v>188</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C126" s="3">
+        <v>407</v>
+      </c>
+      <c r="D126" s="3">
+        <v>528</v>
+      </c>
+      <c r="E126" s="3">
+        <f t="shared" si="8"/>
+        <v>-121</v>
+      </c>
+      <c r="F126" s="3">
+        <v>112</v>
+      </c>
+      <c r="G126" s="3">
+        <v>197</v>
+      </c>
+      <c r="H126" s="3">
+        <f t="shared" si="9"/>
+        <v>188</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C127" s="3">
+        <v>411</v>
+      </c>
+      <c r="D127" s="3">
+        <v>537</v>
+      </c>
+      <c r="E127" s="3">
+        <f t="shared" si="8"/>
+        <v>-126</v>
+      </c>
+      <c r="F127" s="3">
+        <v>112</v>
+      </c>
+      <c r="G127" s="3">
+        <v>201</v>
+      </c>
+      <c r="H127" s="3">
+        <f t="shared" si="9"/>
+        <v>187</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C128" s="3">
+        <v>414</v>
+      </c>
+      <c r="D128" s="3">
+        <v>545</v>
+      </c>
+      <c r="E128" s="3">
+        <f t="shared" si="8"/>
+        <v>-131</v>
+      </c>
+      <c r="F128" s="3">
+        <v>111</v>
+      </c>
+      <c r="G128" s="3">
+        <v>205</v>
+      </c>
+      <c r="H128" s="3">
+        <f t="shared" si="9"/>
+        <v>185</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C129" s="3">
+        <v>414</v>
+      </c>
+      <c r="D129" s="3">
+        <v>556</v>
+      </c>
+      <c r="E129" s="3">
+        <f t="shared" si="8"/>
+        <v>-142</v>
+      </c>
+      <c r="F129" s="3">
+        <v>111</v>
+      </c>
+      <c r="G129" s="3">
+        <v>209</v>
+      </c>
+      <c r="H129" s="3">
+        <f t="shared" si="9"/>
+        <v>178</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C130" s="3">
+        <v>413</v>
+      </c>
+      <c r="D130" s="3">
+        <v>564</v>
+      </c>
+      <c r="E130" s="3">
+        <f t="shared" si="8"/>
+        <v>-151</v>
+      </c>
+      <c r="F130" s="3">
+        <v>110</v>
+      </c>
+      <c r="G130" s="3">
+        <v>212</v>
+      </c>
+      <c r="H130" s="3">
+        <f t="shared" si="9"/>
+        <v>171</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C131" s="3">
+        <v>412</v>
+      </c>
+      <c r="D131" s="3">
+        <v>572</v>
+      </c>
+      <c r="E131" s="3">
+        <f t="shared" si="8"/>
+        <v>-160</v>
+      </c>
+      <c r="F131" s="3">
+        <v>108</v>
+      </c>
+      <c r="G131" s="3">
+        <v>217</v>
+      </c>
+      <c r="H131" s="3">
+        <f t="shared" si="9"/>
+        <v>165</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C132" s="3">
+        <v>412</v>
+      </c>
+      <c r="D132" s="3">
+        <v>581</v>
+      </c>
+      <c r="E132" s="3">
+        <f t="shared" si="8"/>
+        <v>-169</v>
+      </c>
+      <c r="F132" s="3">
+        <v>108</v>
+      </c>
+      <c r="G132" s="3">
+        <v>220</v>
+      </c>
+      <c r="H132" s="3">
+        <f t="shared" si="9"/>
+        <v>159</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A133" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C133" s="3">
+        <v>410</v>
+      </c>
+      <c r="D133" s="3">
+        <v>589</v>
+      </c>
+      <c r="E133" s="3">
+        <f t="shared" si="8"/>
+        <v>-179</v>
+      </c>
+      <c r="F133" s="3">
+        <v>107</v>
+      </c>
+      <c r="G133" s="3">
+        <v>227</v>
+      </c>
+      <c r="H133" s="3">
+        <f t="shared" si="9"/>
+        <v>155</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A134" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C134" s="3">
+        <v>409</v>
+      </c>
+      <c r="D134" s="3">
+        <v>595</v>
+      </c>
+      <c r="E134" s="3">
+        <f t="shared" si="8"/>
+        <v>-186</v>
+      </c>
+      <c r="F134" s="3">
+        <v>105</v>
+      </c>
+      <c r="G134" s="3">
+        <v>231</v>
+      </c>
+      <c r="H134" s="3">
+        <f t="shared" si="9"/>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C135" s="3">
+        <v>406</v>
+      </c>
+      <c r="D135" s="3">
+        <v>601</v>
+      </c>
+      <c r="E135" s="3">
+        <f t="shared" si="8"/>
+        <v>-195</v>
+      </c>
+      <c r="F135" s="3">
+        <v>105</v>
+      </c>
+      <c r="G135" s="3">
+        <v>236</v>
+      </c>
+      <c r="H135" s="3">
+        <f t="shared" si="9"/>
+        <v>146</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A136" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C136" s="3">
+        <v>404</v>
+      </c>
+      <c r="D136" s="3">
+        <v>606</v>
+      </c>
+      <c r="E136" s="3">
+        <f t="shared" si="8"/>
+        <v>-202</v>
+      </c>
+      <c r="F136" s="3">
+        <v>103</v>
+      </c>
+      <c r="G136" s="3">
+        <v>240</v>
+      </c>
+      <c r="H136" s="3">
+        <f t="shared" si="9"/>
+        <v>141</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A137" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C137" s="3">
+        <v>401</v>
+      </c>
+      <c r="D137" s="3">
+        <v>611</v>
+      </c>
+      <c r="E137" s="3">
+        <f t="shared" si="8"/>
+        <v>-210</v>
+      </c>
+      <c r="F137" s="3">
+        <v>102</v>
+      </c>
+      <c r="G137" s="3">
+        <v>243</v>
+      </c>
+      <c r="H137" s="3">
+        <f t="shared" si="9"/>
+        <v>135</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A138" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C138" s="3">
+        <v>398</v>
+      </c>
+      <c r="D138" s="3">
+        <v>614</v>
+      </c>
+      <c r="E138" s="3">
+        <f t="shared" si="8"/>
+        <v>-216</v>
+      </c>
+      <c r="F138" s="3">
+        <v>101</v>
+      </c>
+      <c r="G138" s="3">
+        <v>245</v>
+      </c>
+      <c r="H138" s="3">
+        <f t="shared" si="9"/>
+        <v>130</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A139" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C139" s="3">
+        <v>396</v>
+      </c>
+      <c r="D139" s="3">
+        <v>618</v>
+      </c>
+      <c r="E139" s="3">
+        <f t="shared" si="8"/>
+        <v>-222</v>
+      </c>
+      <c r="F139" s="3">
+        <v>99</v>
+      </c>
+      <c r="G139" s="3">
+        <v>246</v>
+      </c>
+      <c r="H139" s="3">
+        <f t="shared" si="9"/>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A140" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C140" s="3">
+        <v>391</v>
+      </c>
+      <c r="D140" s="3">
+        <v>621</v>
+      </c>
+      <c r="E140" s="3">
+        <f t="shared" si="8"/>
+        <v>-230</v>
+      </c>
+      <c r="F140" s="3">
+        <v>99</v>
+      </c>
+      <c r="G140" s="3">
+        <v>246</v>
+      </c>
+      <c r="H140" s="3">
+        <f t="shared" si="9"/>
+        <v>115</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A141" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C141" s="3">
+        <v>389</v>
+      </c>
+      <c r="D141" s="3">
+        <v>624</v>
+      </c>
+      <c r="E141" s="3">
+        <f t="shared" si="8"/>
+        <v>-235</v>
+      </c>
+      <c r="F141" s="3">
+        <v>97</v>
+      </c>
+      <c r="G141" s="3">
+        <v>245</v>
+      </c>
+      <c r="H141" s="3">
+        <f t="shared" si="9"/>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A142" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C142" s="3">
+        <v>386</v>
+      </c>
+      <c r="D142" s="3">
+        <v>626</v>
+      </c>
+      <c r="E142" s="3">
+        <f t="shared" si="8"/>
+        <v>-240</v>
+      </c>
+      <c r="F142" s="3">
+        <v>97</v>
+      </c>
+      <c r="G142" s="3">
+        <v>243</v>
+      </c>
+      <c r="H142" s="3">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A143" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C143" s="3">
+        <v>383</v>
+      </c>
+      <c r="D143" s="3">
+        <v>628</v>
+      </c>
+      <c r="E143" s="3">
+        <f t="shared" si="8"/>
+        <v>-245</v>
+      </c>
+      <c r="F143" s="3">
+        <v>95</v>
+      </c>
+      <c r="G143" s="3">
+        <v>241</v>
+      </c>
+      <c r="H143" s="3">
+        <f t="shared" si="9"/>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B144" s="2"/>
+      <c r="C144" s="3">
+        <f>SUM(C119:C143)</f>
+        <v>10007</v>
+      </c>
+      <c r="D144" s="3">
+        <f>SUM(D119:D143)</f>
+        <v>14100</v>
+      </c>
+      <c r="E144" s="3">
+        <f>SUM(E119:E143)</f>
+        <v>-4093</v>
+      </c>
+      <c r="F144" s="3">
+        <f>SUM(F119:F143)</f>
+        <v>2518</v>
+      </c>
+      <c r="G144" s="3">
+        <f>SUM(G119:G143)</f>
+        <v>5188</v>
+      </c>
+      <c r="H144" s="3">
+        <f t="shared" si="9"/>
+        <v>3613</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A145" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C145" s="3">
+        <v>197</v>
+      </c>
+      <c r="D145" s="3">
+        <v>278</v>
+      </c>
+      <c r="E145" s="3">
+        <f t="shared" si="8"/>
+        <v>-81</v>
+      </c>
+      <c r="F145" s="3">
+        <v>94</v>
+      </c>
+      <c r="G145" s="3">
+        <v>106</v>
+      </c>
+      <c r="H145" s="3">
+        <f t="shared" si="9"/>
+        <v>119</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A146" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C146" s="3">
+        <v>199</v>
+      </c>
+      <c r="D146" s="3">
+        <v>281</v>
+      </c>
+      <c r="E146" s="3">
+        <f t="shared" si="8"/>
+        <v>-82</v>
+      </c>
+      <c r="F146" s="3">
+        <v>90</v>
+      </c>
+      <c r="G146" s="3">
+        <v>106</v>
+      </c>
+      <c r="H146" s="3">
+        <f t="shared" si="9"/>
+        <v>114</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A147" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C147" s="3">
+        <v>199</v>
+      </c>
+      <c r="D147" s="3">
+        <v>282</v>
+      </c>
+      <c r="E147" s="3">
+        <f t="shared" si="8"/>
+        <v>-83</v>
+      </c>
+      <c r="F147" s="3">
+        <v>86</v>
+      </c>
+      <c r="G147" s="3">
+        <v>109</v>
+      </c>
+      <c r="H147" s="3">
+        <f t="shared" si="9"/>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A148" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C148" s="3">
+        <v>201</v>
+      </c>
+      <c r="D148" s="3">
+        <v>286</v>
+      </c>
+      <c r="E148" s="3">
+        <f t="shared" si="8"/>
+        <v>-85</v>
+      </c>
+      <c r="F148" s="3">
+        <v>82</v>
+      </c>
+      <c r="G148" s="3">
+        <v>112</v>
+      </c>
+      <c r="H148" s="3">
+        <f t="shared" si="9"/>
+        <v>109</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A149" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C149" s="3">
+        <v>202</v>
+      </c>
+      <c r="D149" s="3">
+        <v>290</v>
+      </c>
+      <c r="E149" s="3">
+        <f t="shared" ref="E149:E169" si="10">C149-D149</f>
+        <v>-88</v>
+      </c>
+      <c r="F149" s="3">
+        <v>79</v>
+      </c>
+      <c r="G149" s="3">
+        <v>116</v>
+      </c>
+      <c r="H149" s="3">
+        <f t="shared" si="9"/>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A150" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C150" s="3">
+        <v>205</v>
+      </c>
+      <c r="D150" s="3">
+        <v>295</v>
+      </c>
+      <c r="E150" s="3">
+        <f t="shared" si="10"/>
+        <v>-90</v>
+      </c>
+      <c r="F150" s="3">
+        <v>74</v>
+      </c>
+      <c r="G150" s="3">
+        <v>120</v>
+      </c>
+      <c r="H150" s="3">
+        <f t="shared" si="9"/>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A151" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C151" s="3">
+        <v>205</v>
+      </c>
+      <c r="D151" s="3">
+        <v>299</v>
+      </c>
+      <c r="E151" s="3">
+        <f t="shared" si="10"/>
+        <v>-94</v>
+      </c>
+      <c r="F151" s="3">
+        <v>73</v>
+      </c>
+      <c r="G151" s="3">
+        <v>125</v>
+      </c>
+      <c r="H151" s="3">
+        <f t="shared" si="9"/>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A152" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C152" s="3">
+        <v>209</v>
+      </c>
+      <c r="D152" s="3">
+        <v>305</v>
+      </c>
+      <c r="E152" s="3">
+        <f t="shared" si="10"/>
+        <v>-96</v>
+      </c>
+      <c r="F152" s="3">
+        <v>74</v>
+      </c>
+      <c r="G152" s="3">
+        <v>128</v>
+      </c>
+      <c r="H152" s="3">
+        <f t="shared" si="9"/>
+        <v>106</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A153" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C153" s="3">
+        <v>210</v>
+      </c>
+      <c r="D153" s="3">
+        <v>310</v>
+      </c>
+      <c r="E153" s="3">
+        <f t="shared" si="10"/>
+        <v>-100</v>
+      </c>
+      <c r="F153" s="3">
+        <v>74</v>
+      </c>
+      <c r="G153" s="3">
+        <v>133</v>
+      </c>
+      <c r="H153" s="3">
+        <f t="shared" si="9"/>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A154" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C154" s="3">
+        <v>212</v>
+      </c>
+      <c r="D154" s="3">
+        <v>315</v>
+      </c>
+      <c r="E154" s="3">
+        <f t="shared" si="10"/>
+        <v>-103</v>
+      </c>
+      <c r="F154" s="3">
+        <v>74</v>
+      </c>
+      <c r="G154" s="3">
+        <v>137</v>
+      </c>
+      <c r="H154" s="3">
+        <f t="shared" si="9"/>
+        <v>108</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A155" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C155" s="3">
+        <v>213</v>
+      </c>
+      <c r="D155" s="3">
+        <v>321</v>
+      </c>
+      <c r="E155" s="3">
+        <f t="shared" si="10"/>
+        <v>-108</v>
+      </c>
+      <c r="F155" s="3">
+        <v>74</v>
+      </c>
+      <c r="G155" s="3">
+        <v>141</v>
+      </c>
+      <c r="H155" s="3">
+        <f t="shared" si="9"/>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A156" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C156" s="3">
+        <v>213</v>
+      </c>
+      <c r="D156" s="3">
+        <v>325</v>
+      </c>
+      <c r="E156" s="3">
+        <f t="shared" si="10"/>
+        <v>-112</v>
+      </c>
+      <c r="F156" s="3">
+        <v>72</v>
+      </c>
+      <c r="G156" s="3">
+        <v>144</v>
+      </c>
+      <c r="H156" s="3">
+        <f t="shared" si="9"/>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A157" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C157" s="3">
+        <v>213</v>
+      </c>
+      <c r="D157" s="3">
+        <v>331</v>
+      </c>
+      <c r="E157" s="3">
+        <f t="shared" si="10"/>
+        <v>-118</v>
+      </c>
+      <c r="F157" s="3">
+        <v>72</v>
+      </c>
+      <c r="G157" s="3">
+        <v>147</v>
+      </c>
+      <c r="H157" s="3">
+        <f t="shared" si="9"/>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A158" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C158" s="3">
+        <v>213</v>
+      </c>
+      <c r="D158" s="3">
+        <v>336</v>
+      </c>
+      <c r="E158" s="3">
+        <f t="shared" si="10"/>
+        <v>-123</v>
+      </c>
+      <c r="F158" s="3">
+        <v>72</v>
+      </c>
+      <c r="G158" s="3">
+        <v>150</v>
+      </c>
+      <c r="H158" s="3">
+        <f t="shared" si="9"/>
+        <v>99</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A159" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C159" s="3">
+        <v>213</v>
+      </c>
+      <c r="D159" s="3">
+        <v>339</v>
+      </c>
+      <c r="E159" s="3">
+        <f t="shared" si="10"/>
+        <v>-126</v>
+      </c>
+      <c r="F159" s="3">
+        <v>70</v>
+      </c>
+      <c r="G159" s="3">
+        <v>152</v>
+      </c>
+      <c r="H159" s="3">
+        <f t="shared" si="9"/>
+        <v>96</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A160" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C160" s="3">
+        <v>213</v>
+      </c>
+      <c r="D160" s="3">
+        <v>344</v>
+      </c>
+      <c r="E160" s="3">
+        <f t="shared" si="10"/>
+        <v>-131</v>
+      </c>
+      <c r="F160" s="3">
+        <v>70</v>
+      </c>
+      <c r="G160" s="3">
+        <v>154</v>
+      </c>
+      <c r="H160" s="3">
+        <f t="shared" si="9"/>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A161" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C161" s="3">
+        <v>211</v>
+      </c>
+      <c r="D161" s="3">
+        <v>347</v>
+      </c>
+      <c r="E161" s="3">
+        <f t="shared" si="10"/>
+        <v>-136</v>
+      </c>
+      <c r="F161" s="3">
+        <v>70</v>
+      </c>
+      <c r="G161" s="3">
+        <v>156</v>
+      </c>
+      <c r="H161" s="3">
+        <f t="shared" si="9"/>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A162" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C162" s="3">
+        <v>211</v>
+      </c>
+      <c r="D162" s="3">
+        <v>351</v>
+      </c>
+      <c r="E162" s="3">
+        <f t="shared" si="10"/>
+        <v>-140</v>
+      </c>
+      <c r="F162" s="3">
+        <v>68</v>
+      </c>
+      <c r="G162" s="3">
+        <v>159</v>
+      </c>
+      <c r="H162" s="3">
+        <f t="shared" si="9"/>
+        <v>87</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A163" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C163" s="3">
+        <v>209</v>
+      </c>
+      <c r="D163" s="3">
+        <v>354</v>
+      </c>
+      <c r="E163" s="3">
+        <f t="shared" si="10"/>
+        <v>-145</v>
+      </c>
+      <c r="F163" s="3">
+        <v>68</v>
+      </c>
+      <c r="G163" s="3">
+        <v>159</v>
+      </c>
+      <c r="H163" s="3">
+        <f t="shared" si="9"/>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A164" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C164" s="3">
+        <v>209</v>
+      </c>
+      <c r="D164" s="3">
+        <v>357</v>
+      </c>
+      <c r="E164" s="3">
+        <f t="shared" si="10"/>
+        <v>-148</v>
+      </c>
+      <c r="F164" s="3">
+        <v>67</v>
+      </c>
+      <c r="G164" s="3">
+        <v>160</v>
+      </c>
+      <c r="H164" s="3">
+        <f t="shared" si="9"/>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A165" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C165" s="3">
+        <v>206</v>
+      </c>
+      <c r="D165" s="3">
+        <v>359</v>
+      </c>
+      <c r="E165" s="3">
+        <f t="shared" si="10"/>
+        <v>-153</v>
+      </c>
+      <c r="F165" s="3">
+        <v>66</v>
+      </c>
+      <c r="G165" s="3">
+        <v>162</v>
+      </c>
+      <c r="H165" s="3">
+        <f t="shared" si="9"/>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A166" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C166" s="3">
+        <v>205</v>
+      </c>
+      <c r="D166" s="3">
+        <v>363</v>
+      </c>
+      <c r="E166" s="3">
+        <f t="shared" si="10"/>
+        <v>-158</v>
+      </c>
+      <c r="F166" s="3">
+        <v>66</v>
+      </c>
+      <c r="G166" s="3">
+        <v>162</v>
+      </c>
+      <c r="H166" s="3">
+        <f t="shared" si="9"/>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A167" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C167" s="3">
+        <v>204</v>
+      </c>
+      <c r="D167" s="3">
+        <v>365</v>
+      </c>
+      <c r="E167" s="3">
+        <f t="shared" si="10"/>
+        <v>-161</v>
+      </c>
+      <c r="F167" s="3">
+        <v>64</v>
+      </c>
+      <c r="G167" s="3">
+        <v>163</v>
+      </c>
+      <c r="H167" s="3">
+        <f t="shared" si="9"/>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A168" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C168" s="3">
+        <v>202</v>
+      </c>
+      <c r="D168" s="3">
+        <v>368</v>
+      </c>
+      <c r="E168" s="3">
+        <f t="shared" si="10"/>
+        <v>-166</v>
+      </c>
+      <c r="F168" s="3">
+        <v>65</v>
+      </c>
+      <c r="G168" s="3">
+        <v>162</v>
+      </c>
+      <c r="H168" s="3">
+        <f t="shared" si="9"/>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A169" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C169" s="3">
+        <v>201</v>
+      </c>
+      <c r="D169" s="3">
+        <v>370</v>
+      </c>
+      <c r="E169" s="3">
+        <f t="shared" si="10"/>
+        <v>-169</v>
+      </c>
+      <c r="F169" s="3">
+        <v>63</v>
+      </c>
+      <c r="G169" s="3">
+        <v>161</v>
+      </c>
+      <c r="H169" s="3">
+        <f t="shared" ref="H169:H170" si="11">E169+F169+G169</f>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C170" s="3">
+        <f>SUM(C145:C169)</f>
+        <v>5175</v>
+      </c>
+      <c r="D170" s="3">
+        <f>SUM(D145:D169)</f>
+        <v>8171</v>
+      </c>
+      <c r="E170" s="3">
+        <f>SUM(E145:E169)</f>
+        <v>-2996</v>
+      </c>
+      <c r="F170" s="3">
+        <f>SUM(F145:F169)</f>
+        <v>1827</v>
+      </c>
+      <c r="G170" s="3">
+        <f>SUM(G145:G169)</f>
+        <v>3524</v>
+      </c>
+      <c r="H170" s="3">
+        <f t="shared" si="11"/>
+        <v>2355</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/01_Befolkning/Befolkningsframskrivinger/Diverse befolkningsframskrivinger.xlsx
+++ b/01_Befolkning/Befolkningsframskrivinger/Diverse befolkningsframskrivinger.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vestfoldfylke-my.sharepoint.com/personal/rasmus_palmqvist_vestfoldfylke_no/Documents/Dokumenter/GitHub/Ny mappe/Vestfold/01_Befolkning/Befolkningsframskrivinger/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="202" documentId="8_{5B31AB13-E86D-463D-90A3-187EE6EE97F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{924246BB-98D1-4B02-950C-5CEA647869E2}"/>
+  <xr:revisionPtr revIDLastSave="203" documentId="8_{5B31AB13-E86D-463D-90A3-187EE6EE97F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6DFBA105-9CC9-47FF-B422-B2E869B4C96B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6321,7 +6321,7 @@
         <v>10.221646383786034</v>
       </c>
       <c r="K10" s="7">
-        <f t="shared" si="4"/>
+        <f>F10/$G10*100</f>
         <v>11.364968457421375</v>
       </c>
     </row>
